--- a/Knowledge/Model Schema/PEP/Model Output/PEP_model_v3.xlsx
+++ b/Knowledge/Model Schema/PEP/Model Output/PEP_model_v3.xlsx
@@ -7,16 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASSUMPTIONS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANNL P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCE SHEET" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASH FLOW" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS DRIVERS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS DRIVERS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF DRIVERS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR BS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR CF" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANNL P&amp;L" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCE SHEET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASH FLOW" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR BS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR CF" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,14 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;--&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0_);($#,##0);&quot;$--&quot;_)"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00_);($#,##0.00)"/>
-    <numFmt numFmtId="167" formatCode="0.0%;(0.0%);&quot;--&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0;(0.0);&quot;--&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,13 +41,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,18 +59,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAEAEA"/>
-        <bgColor rgb="00EAEAEA"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,16 +92,6 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,2292 +457,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Days in Year</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n">
-        <v>365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Used in DSO, DIO, DPO formulas</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Share Repurchases $</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Per-period repurchase assumption for projection</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2022</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2022</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2023</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2023</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2023</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2024</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2024</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2024</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2025</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2025</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2025</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Net Income (Loss)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>4273</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>5719</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>8443</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1944</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>4715</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>7831</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>2053</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>5147</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>8092</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>1843</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>3122</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>5740</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>555</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1854</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>590</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1268</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>641</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1379</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>2118</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>684</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>1491</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>2315</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Gain on Juice Transaction</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>-3322</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>-3335</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-3321</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Impairment and Other Charges</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>482</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1871</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1877</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>1860</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>1960</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Product Recall Impact</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>182</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>184</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Cash Payments for Product Recall</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-135</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>-138</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Operating Lease ROU Asset Amortization</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>346</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>248</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>384</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>278</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>438</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>315</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>489</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Stock-Based Compensation</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>233</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>179</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>267</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>183</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Restructuring and Asset Impairment Charges</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>204</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>287</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>415</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>567</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Cash Payments for Restructuring</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>-32</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-82</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-134</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-64</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>-187</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>-283</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>-173</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>-284</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-232</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>-387</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>-554</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>-145</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Acquisition and Divestiture-Related Charges</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>308</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>-113</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Cash Payments for Acquisition and Divestiture Costs</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>-34</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>-41</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>-80</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Pension and Postretirement Benefits Expense</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>164</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Pension and Postretirement Benefits Contributions</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>-178</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-214</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-335</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-175</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>-209</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-374</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>-218</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>-263</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>-300</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>-317</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>-354</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>-400</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>-270</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>(Benefit) Provision for Deferred Income Taxes</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-322</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>343</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>-260</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Tax Expense Related to TCJ Act</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Tax Payments Related to TCJ Act</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-309</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-309</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>-309</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>-309</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>-579</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>-579</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>-772</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>-772</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>-837</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-1753</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-2258</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-348</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>-1330</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>-1699</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>-96</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>-1138</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>-1521</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>-318</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>-1582</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>-1747</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>-530</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>-549</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-990</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-837</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-542</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>-851</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>-473</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>-291</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>-696</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>-492</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>-238</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>-800</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>-449</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>-315</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Prepaid Expenses</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>-190</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-186</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-124</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-288</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>-271</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-242</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>-342</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>-365</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>-200</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>-307</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>-354</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>-223</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>-406</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>-1238</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-990</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-2259</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>-1960</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>-859</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>-3408</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>-2968</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>-2312</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-2671</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>-2083</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>-1647</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>-1847</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>489</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>608</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>718</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>512</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>287</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>415</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Other Operating Items</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>-133</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-325</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-426</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>-68</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>-203</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>-135</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-232</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>-269</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>-441</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>-157</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Cash Flow from Operations</t>
-        </is>
-      </c>
-      <c r="B25" s="6">
-        <f>SUM(B2:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="6">
-        <f>SUM(C2:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="6">
-        <f>SUM(D2:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="6">
-        <f>SUM(E2:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="6">
-        <f>SUM(F2:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="6">
-        <f>SUM(G2:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="6">
-        <f>SUM(H2:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="6">
-        <f>SUM(I2:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="6">
-        <f>SUM(J2:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="6">
-        <f>SUM(K2:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="6">
-        <f>SUM(L2:L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="6">
-        <f>SUM(M2:M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="6">
-        <f>SUM(N2:N24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Purchase of PP&amp;E</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>-522</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-1499</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-2556</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-581</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>-1513</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>-614</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>-1701</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>-2850</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>-603</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>-1507</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>-2499</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>-447</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Sale of Assets</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>228</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>177</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Acquisitions, Net of Cash Acquired</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>-29</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>-804</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>-83</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>-31</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>-3130</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>-3176</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>-67</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Juice Transaction</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>3456</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>3456</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>3456</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Divestitures of Businesses</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Net Change in Short-Term Investments</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-37</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-39</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>-56</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>-421</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>441</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>447</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>278</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Other Investing Activities</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>-111</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>-117</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Cash Flow from Investing</t>
-        </is>
-      </c>
-      <c r="B33" s="6">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="6">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="6">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="6">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="6">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="6">
-        <f>SUM(G26:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="6">
-        <f>SUM(H26:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="6">
-        <f>SUM(I26:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="6">
-        <f>SUM(J26:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="6">
-        <f>SUM(K26:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="6">
-        <f>SUM(L26:L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="6">
-        <f>SUM(M26:M32)</f>
-        <v/>
-      </c>
-      <c r="N33" s="6">
-        <f>SUM(N26:N32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Issuance of Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>3377</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>2986</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>2986</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2986</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>1761</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>1765</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>4014</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>3505</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>3521</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>8179</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>2964</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Repayments of Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>-1251</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-3202</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-3203</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-1251</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>-2252</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>-2253</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>-1252</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>-2882</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>-2883</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>-1541</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>-2543</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>-3245</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>-1629</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Short-Term Debt</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>559</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>1935</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1947</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>393</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>1660</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>4688</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2313</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>3080</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>3808</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>3656</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>5251</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>5528</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Repayments of Short-Term Debt</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-1932</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>-26</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>-1037</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>-1631</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>-2138</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>-4177</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>-2119</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>-2492</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>-5417</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>-676</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Net Change in Other Short-Term Debt</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>647</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>844</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-45</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>491</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>1395</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>774</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>1286</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>373</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>2438</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>445</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Common Dividends</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>-1505</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-2997</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-4586</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-1608</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>-3199</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>-4941</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>-1767</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>-3506</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>-5369</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>-1882</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>-3743</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>-5692</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>-1966</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Share Repurchases</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>-193</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>-699</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>-1156</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>-160</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>-453</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>-751</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>-146</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>-461</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>-760</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>-183</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>-494</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>-752</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>-182</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Exercise of Stock Options</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Tax Withholdings on RSU/PSU Settlement</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>-85</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>-87</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-97</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>-116</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>-119</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>-135</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>-131</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>-132</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>-89</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>-111</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>-112</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Other Financing Activities</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Cash Flow from Financing</t>
-        </is>
-      </c>
-      <c r="B44" s="6">
-        <f>SUM(B34:B43)</f>
-        <v/>
-      </c>
-      <c r="C44" s="6">
-        <f>SUM(C34:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="6">
-        <f>SUM(D34:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="6">
-        <f>SUM(E34:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="6">
-        <f>SUM(F34:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="6">
-        <f>SUM(G34:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="6">
-        <f>SUM(H34:H43)</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>SUM(I34:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="6">
-        <f>SUM(J34:J43)</f>
-        <v/>
-      </c>
-      <c r="K44" s="6">
-        <f>SUM(K34:K43)</f>
-        <v/>
-      </c>
-      <c r="L44" s="6">
-        <f>SUM(L34:L43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="6">
-        <f>SUM(M34:M43)</f>
-        <v/>
-      </c>
-      <c r="N44" s="6">
-        <f>SUM(N34:N43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>FX Effect on Cash</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-83</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-197</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-116</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>-254</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>-38</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>-304</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>-391</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>203</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>422</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>395</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Net Change in Cash</t>
-        </is>
-      </c>
-      <c r="B46" s="6">
-        <f>B25+B33+B44+B45+B46</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>C25+C33+C44+C45+C46</f>
-        <v/>
-      </c>
-      <c r="D46" s="6">
-        <f>D25+D33+D44+D45+D46</f>
-        <v/>
-      </c>
-      <c r="E46" s="6">
-        <f>E25+E33+E44+E45+E46</f>
-        <v/>
-      </c>
-      <c r="F46" s="6">
-        <f>F25+F33+F44+F45+F46</f>
-        <v/>
-      </c>
-      <c r="G46" s="6">
-        <f>G25+G33+G44+G45+G46</f>
-        <v/>
-      </c>
-      <c r="H46" s="6">
-        <f>H25+H33+H44+H45+H46</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>I25+I33+I44+I45+I46</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>J25+J33+J44+J45+J46</f>
-        <v/>
-      </c>
-      <c r="K46" s="6">
-        <f>K25+K33+K44+K45+K46</f>
-        <v/>
-      </c>
-      <c r="L46" s="6">
-        <f>L25+L33+L44+L45+L46</f>
-        <v/>
-      </c>
-      <c r="M46" s="6">
-        <f>M25+M33+M44+M45+M46</f>
-        <v/>
-      </c>
-      <c r="N46" s="6">
-        <f>N25+N33+N44+N45+N46</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2872,30 +553,12 @@
       <c r="F2" s="4" t="n">
         <v>93925</v>
       </c>
-      <c r="G2" s="12">
-        <f>'ANNL P&amp;L'!F2*(1+'IS DRIVERS'!G2)</f>
-        <v/>
-      </c>
-      <c r="H2" s="12">
-        <f>'ANNL P&amp;L'!G2*(1+'IS DRIVERS'!H2)</f>
-        <v/>
-      </c>
-      <c r="I2" s="12">
-        <f>'ANNL P&amp;L'!H2*(1+'IS DRIVERS'!I2)</f>
-        <v/>
-      </c>
-      <c r="J2" s="12">
-        <f>'ANNL P&amp;L'!I2*(1+'IS DRIVERS'!J2)</f>
-        <v/>
-      </c>
-      <c r="K2" s="12">
-        <f>'ANNL P&amp;L'!J2*(1+'IS DRIVERS'!K2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="12">
-        <f>'ANNL P&amp;L'!K2*(1+'IS DRIVERS'!L2)</f>
-        <v/>
-      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2918,30 +581,12 @@
       <c r="F3" s="4" t="n">
         <v>-43066</v>
       </c>
-      <c r="G3" s="12">
-        <f>'IS DRIVERS'!G3*'ANNL P&amp;L'!G2</f>
-        <v/>
-      </c>
-      <c r="H3" s="12">
-        <f>'IS DRIVERS'!H3*'ANNL P&amp;L'!H2</f>
-        <v/>
-      </c>
-      <c r="I3" s="12">
-        <f>'IS DRIVERS'!I3*'ANNL P&amp;L'!I2</f>
-        <v/>
-      </c>
-      <c r="J3" s="12">
-        <f>'IS DRIVERS'!J3*'ANNL P&amp;L'!J2</f>
-        <v/>
-      </c>
-      <c r="K3" s="12">
-        <f>'IS DRIVERS'!K3*'ANNL P&amp;L'!K2</f>
-        <v/>
-      </c>
-      <c r="L3" s="12">
-        <f>'IS DRIVERS'!L3*'ANNL P&amp;L'!L2</f>
-        <v/>
-      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3015,30 +660,12 @@
       <c r="F5" s="4" t="n">
         <v>-37368</v>
       </c>
-      <c r="G5" s="12">
-        <f>'IS DRIVERS'!G4*'ANNL P&amp;L'!G2</f>
-        <v/>
-      </c>
-      <c r="H5" s="12">
-        <f>'IS DRIVERS'!H4*'ANNL P&amp;L'!H2</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>'IS DRIVERS'!I4*'ANNL P&amp;L'!I2</f>
-        <v/>
-      </c>
-      <c r="J5" s="12">
-        <f>'IS DRIVERS'!J4*'ANNL P&amp;L'!J2</f>
-        <v/>
-      </c>
-      <c r="K5" s="12">
-        <f>'IS DRIVERS'!K4*'ANNL P&amp;L'!K2</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>'IS DRIVERS'!L4*'ANNL P&amp;L'!L2</f>
-        <v/>
-      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3196,30 +823,12 @@
       <c r="F10" s="4" t="n">
         <v>-1121</v>
       </c>
-      <c r="G10" s="12">
-        <f>'IS DRIVERS'!G5</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>'IS DRIVERS'!H5</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>'IS DRIVERS'!I5</f>
-        <v/>
-      </c>
-      <c r="J10" s="12">
-        <f>'IS DRIVERS'!J5</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>'IS DRIVERS'!K5</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>'IS DRIVERS'!L5</f>
-        <v/>
-      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3507,30 +1116,12 @@
       <c r="F18" s="4" t="n">
         <v>1369000000</v>
       </c>
-      <c r="G18" s="12">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="12">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="12">
-        <f>H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="12">
-        <f>I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="12">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="12">
-        <f>K18</f>
-        <v/>
-      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3553,37 +1144,19 @@
       <c r="F19" s="4" t="n">
         <v>1373000000</v>
       </c>
-      <c r="G19" s="12">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="12">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="12">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="12">
-        <f>J19</f>
-        <v/>
-      </c>
-      <c r="L19" s="12">
-        <f>K19</f>
-        <v/>
-      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3676,30 +1249,12 @@
       <c r="E2" s="4" t="n">
         <v>9159</v>
       </c>
-      <c r="F2" s="12">
-        <f>E2+'CASH FLOW'!G48</f>
-        <v/>
-      </c>
-      <c r="G2" s="12">
-        <f>F2+'CASH FLOW'!H48</f>
-        <v/>
-      </c>
-      <c r="H2" s="12">
-        <f>G2+'CASH FLOW'!I48</f>
-        <v/>
-      </c>
-      <c r="I2" s="12">
-        <f>H2+'CASH FLOW'!J48</f>
-        <v/>
-      </c>
-      <c r="J2" s="12">
-        <f>I2+'CASH FLOW'!K48</f>
-        <v/>
-      </c>
-      <c r="K2" s="12">
-        <f>J2+'CASH FLOW'!L48</f>
-        <v/>
-      </c>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3744,30 +1299,12 @@
       <c r="E4" s="4" t="n">
         <v>11506</v>
       </c>
-      <c r="F4" s="12">
-        <f>'BS DRIVERS'!G3*'ANNL P&amp;L'!G2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="G4" s="12">
-        <f>'BS DRIVERS'!H3*'ANNL P&amp;L'!H2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="H4" s="12">
-        <f>'BS DRIVERS'!I3*'ANNL P&amp;L'!I2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="I4" s="12">
-        <f>'BS DRIVERS'!J3*'ANNL P&amp;L'!J2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="J4" s="12">
-        <f>'BS DRIVERS'!K3*'ANNL P&amp;L'!K2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="K4" s="12">
-        <f>'BS DRIVERS'!L3*'ANNL P&amp;L'!L2/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3787,30 +1324,12 @@
       <c r="E5" s="4" t="n">
         <v>5845</v>
       </c>
-      <c r="F5" s="12">
-        <f>'BS DRIVERS'!G4*'ANNL P&amp;L'!G3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="G5" s="12">
-        <f>'BS DRIVERS'!H4*'ANNL P&amp;L'!H3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="H5" s="12">
-        <f>'BS DRIVERS'!I4*'ANNL P&amp;L'!I3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>'BS DRIVERS'!J4*'ANNL P&amp;L'!J3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="J5" s="12">
-        <f>'BS DRIVERS'!K4*'ANNL P&amp;L'!K3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
-      <c r="K5" s="12">
-        <f>'BS DRIVERS'!L4*'ANNL P&amp;L'!L3/ASSUMPTIONS!$B$2</f>
-        <v/>
-      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3830,30 +1349,12 @@
       <c r="E6" s="4" t="n">
         <v>1068</v>
       </c>
-      <c r="F6" s="12">
-        <f>'BS DRIVERS'!G7*'ANNL P&amp;L'!G2</f>
-        <v/>
-      </c>
-      <c r="G6" s="12">
-        <f>'BS DRIVERS'!H7*'ANNL P&amp;L'!H2</f>
-        <v/>
-      </c>
-      <c r="H6" s="12">
-        <f>'BS DRIVERS'!I7*'ANNL P&amp;L'!I2</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>'BS DRIVERS'!J7*'ANNL P&amp;L'!J2</f>
-        <v/>
-      </c>
-      <c r="J6" s="12">
-        <f>'BS DRIVERS'!K7*'ANNL P&amp;L'!K2</f>
-        <v/>
-      </c>
-      <c r="K6" s="12">
-        <f>'BS DRIVERS'!L7*'ANNL P&amp;L'!L2</f>
-        <v/>
-      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3920,30 +1421,12 @@
       <c r="E8" s="4" t="n">
         <v>29905</v>
       </c>
-      <c r="F8" s="12">
-        <f>E8-'CASH FLOW'!G27-'CASH FLOW'!G3</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>F8-'CASH FLOW'!H27-'CASH FLOW'!H3</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
-        <f>G8-'CASH FLOW'!I27-'CASH FLOW'!I3</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>H8-'CASH FLOW'!J27-'CASH FLOW'!J3</f>
-        <v/>
-      </c>
-      <c r="J8" s="12">
-        <f>I8-'CASH FLOW'!K27-'CASH FLOW'!K3</f>
-        <v/>
-      </c>
-      <c r="K8" s="12">
-        <f>J8-'CASH FLOW'!L27-'CASH FLOW'!L3</f>
-        <v/>
-      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3963,30 +1446,12 @@
       <c r="E9" s="4" t="n">
         <v>15066</v>
       </c>
-      <c r="F9" s="12">
-        <f>E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="12">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="12">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="12">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="12">
-        <f>J9</f>
-        <v/>
-      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4006,30 +1471,12 @@
       <c r="E10" s="4" t="n">
         <v>18916</v>
       </c>
-      <c r="F10" s="12">
-        <f>E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="12">
-        <f>F10</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="12">
-        <f>I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>J10</f>
-        <v/>
-      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4074,30 +1521,12 @@
       <c r="E12" s="4" t="n">
         <v>4541</v>
       </c>
-      <c r="F12" s="12">
-        <f>E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="12">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="12">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="12">
-        <f>I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="12">
-        <f>J12</f>
-        <v/>
-      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4117,30 +1546,12 @@
       <c r="E13" s="4" t="n">
         <v>8984</v>
       </c>
-      <c r="F13" s="12">
-        <f>'BS DRIVERS'!G9*'ANNL P&amp;L'!G2</f>
-        <v/>
-      </c>
-      <c r="G13" s="12">
-        <f>'BS DRIVERS'!H9*'ANNL P&amp;L'!H2</f>
-        <v/>
-      </c>
-      <c r="H13" s="12">
-        <f>'BS DRIVERS'!I9*'ANNL P&amp;L'!I2</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>'BS DRIVERS'!J9*'ANNL P&amp;L'!J2</f>
-        <v/>
-      </c>
-      <c r="J13" s="12">
-        <f>'BS DRIVERS'!K9*'ANNL P&amp;L'!K2</f>
-        <v/>
-      </c>
-      <c r="K13" s="12">
-        <f>'BS DRIVERS'!L9*'ANNL P&amp;L'!L2</f>
-        <v/>
-      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4232,30 +1643,12 @@
       <c r="E16" s="4" t="n">
         <v>25903</v>
       </c>
-      <c r="F16" s="12">
-        <f>'BS DRIVERS'!G12*'ANNL P&amp;L'!G2</f>
-        <v/>
-      </c>
-      <c r="G16" s="12">
-        <f>'BS DRIVERS'!H12*'ANNL P&amp;L'!H2</f>
-        <v/>
-      </c>
-      <c r="H16" s="12">
-        <f>'BS DRIVERS'!I12*'ANNL P&amp;L'!I2</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>'BS DRIVERS'!J12*'ANNL P&amp;L'!J2</f>
-        <v/>
-      </c>
-      <c r="J16" s="12">
-        <f>'BS DRIVERS'!K12*'ANNL P&amp;L'!K2</f>
-        <v/>
-      </c>
-      <c r="K16" s="12">
-        <f>'BS DRIVERS'!L12*'ANNL P&amp;L'!L2</f>
-        <v/>
-      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -4347,30 +1740,12 @@
       <c r="E19" s="4" t="n">
         <v>3802</v>
       </c>
-      <c r="F19" s="12">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="12">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="12">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="12">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="12">
-        <f>J19</f>
-        <v/>
-      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4462,30 +1837,12 @@
       <c r="E22" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F22" s="12">
-        <f>E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="12">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="12">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="12">
-        <f>I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>J22</f>
-        <v/>
-      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4505,30 +1862,12 @@
       <c r="E23" s="4" t="n">
         <v>4451</v>
       </c>
-      <c r="F23" s="12">
-        <f>E23+'CASH FLOW'!G10+'CASH FLOW'!G43</f>
-        <v/>
-      </c>
-      <c r="G23" s="12">
-        <f>F23+'CASH FLOW'!H10+'CASH FLOW'!H43</f>
-        <v/>
-      </c>
-      <c r="H23" s="12">
-        <f>G23+'CASH FLOW'!I10+'CASH FLOW'!I43</f>
-        <v/>
-      </c>
-      <c r="I23" s="12">
-        <f>H23+'CASH FLOW'!J10+'CASH FLOW'!J43</f>
-        <v/>
-      </c>
-      <c r="J23" s="12">
-        <f>I23+'CASH FLOW'!K10+'CASH FLOW'!K43</f>
-        <v/>
-      </c>
-      <c r="K23" s="12">
-        <f>J23+'CASH FLOW'!L10+'CASH FLOW'!L43</f>
-        <v/>
-      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4548,30 +1887,12 @@
       <c r="E24" s="4" t="n">
         <v>72788</v>
       </c>
-      <c r="F24" s="12">
-        <f>E24+'ANNL P&amp;L'!G13+'CASH FLOW'!G41</f>
-        <v/>
-      </c>
-      <c r="G24" s="12">
-        <f>F24+'ANNL P&amp;L'!H13+'CASH FLOW'!H41</f>
-        <v/>
-      </c>
-      <c r="H24" s="12">
-        <f>G24+'ANNL P&amp;L'!I13+'CASH FLOW'!I41</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>H24+'ANNL P&amp;L'!J13+'CASH FLOW'!J41</f>
-        <v/>
-      </c>
-      <c r="J24" s="12">
-        <f>I24+'ANNL P&amp;L'!K13+'CASH FLOW'!K41</f>
-        <v/>
-      </c>
-      <c r="K24" s="12">
-        <f>J24+'ANNL P&amp;L'!L13+'CASH FLOW'!L41</f>
-        <v/>
-      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4591,30 +1912,12 @@
       <c r="E25" s="4" t="n">
         <v>-15024</v>
       </c>
-      <c r="F25" s="12">
-        <f>E25+'CASH FLOW'!G47</f>
-        <v/>
-      </c>
-      <c r="G25" s="12">
-        <f>F25+'CASH FLOW'!H47</f>
-        <v/>
-      </c>
-      <c r="H25" s="12">
-        <f>G25+'CASH FLOW'!I47</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>H25+'CASH FLOW'!J47</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>I25+'CASH FLOW'!K47</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>J25+'CASH FLOW'!L47</f>
-        <v/>
-      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4765,7 +2068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4867,30 +2170,12 @@
       <c r="F2" s="4" t="n">
         <v>8295</v>
       </c>
-      <c r="G2" s="12">
-        <f>'ANNL P&amp;L'!G13</f>
-        <v/>
-      </c>
-      <c r="H2" s="12">
-        <f>'ANNL P&amp;L'!H13</f>
-        <v/>
-      </c>
-      <c r="I2" s="12">
-        <f>'ANNL P&amp;L'!I13</f>
-        <v/>
-      </c>
-      <c r="J2" s="12">
-        <f>'ANNL P&amp;L'!J13</f>
-        <v/>
-      </c>
-      <c r="K2" s="12">
-        <f>'ANNL P&amp;L'!K13</f>
-        <v/>
-      </c>
-      <c r="L2" s="12">
-        <f>'ANNL P&amp;L'!L13</f>
-        <v/>
-      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4913,30 +2198,12 @@
       <c r="F3" s="4" t="n">
         <v>3451</v>
       </c>
-      <c r="G3" s="12">
-        <f>'CF DRIVERS'!G3*'BALANCE SHEET'!E8</f>
-        <v/>
-      </c>
-      <c r="H3" s="12">
-        <f>'CF DRIVERS'!H3*'BALANCE SHEET'!F8</f>
-        <v/>
-      </c>
-      <c r="I3" s="12">
-        <f>'CF DRIVERS'!I3*'BALANCE SHEET'!G8</f>
-        <v/>
-      </c>
-      <c r="J3" s="12">
-        <f>'CF DRIVERS'!J3*'BALANCE SHEET'!H8</f>
-        <v/>
-      </c>
-      <c r="K3" s="12">
-        <f>'CF DRIVERS'!K3*'BALANCE SHEET'!I8</f>
-        <v/>
-      </c>
-      <c r="L3" s="12">
-        <f>'CF DRIVERS'!L3*'BALANCE SHEET'!J8</f>
-        <v/>
-      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -5127,30 +2394,12 @@
       <c r="F10" s="4" t="n">
         <v>288</v>
       </c>
-      <c r="G10" s="12">
-        <f>'CF DRIVERS'!G4</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>'CF DRIVERS'!H4</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>'CF DRIVERS'!I4</f>
-        <v/>
-      </c>
-      <c r="J10" s="12">
-        <f>'CF DRIVERS'!J4</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>'CF DRIVERS'!K4</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>'CF DRIVERS'!L4</f>
-        <v/>
-      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5341,30 +2590,12 @@
       <c r="F17" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="G17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -5443,30 +2674,12 @@
       <c r="F20" s="4" t="n">
         <v>-580</v>
       </c>
-      <c r="G20" s="12">
-        <f>-('BALANCE SHEET'!F4-'BALANCE SHEET'!E4)</f>
-        <v/>
-      </c>
-      <c r="H20" s="12">
-        <f>-('BALANCE SHEET'!G4-'BALANCE SHEET'!F4)</f>
-        <v/>
-      </c>
-      <c r="I20" s="12">
-        <f>-('BALANCE SHEET'!H4-'BALANCE SHEET'!G4)</f>
-        <v/>
-      </c>
-      <c r="J20" s="12">
-        <f>-('BALANCE SHEET'!I4-'BALANCE SHEET'!H4)</f>
-        <v/>
-      </c>
-      <c r="K20" s="12">
-        <f>-('BALANCE SHEET'!J4-'BALANCE SHEET'!I4)</f>
-        <v/>
-      </c>
-      <c r="L20" s="12">
-        <f>-('BALANCE SHEET'!K4-'BALANCE SHEET'!J4)</f>
-        <v/>
-      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -5489,30 +2702,12 @@
       <c r="F21" s="4" t="n">
         <v>-150</v>
       </c>
-      <c r="G21" s="12">
-        <f>-('BALANCE SHEET'!F5-'BALANCE SHEET'!E5)</f>
-        <v/>
-      </c>
-      <c r="H21" s="12">
-        <f>-('BALANCE SHEET'!G5-'BALANCE SHEET'!F5)</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>-('BALANCE SHEET'!H5-'BALANCE SHEET'!G5)</f>
-        <v/>
-      </c>
-      <c r="J21" s="12">
-        <f>-('BALANCE SHEET'!I5-'BALANCE SHEET'!H5)</f>
-        <v/>
-      </c>
-      <c r="K21" s="12">
-        <f>-('BALANCE SHEET'!J5-'BALANCE SHEET'!I5)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12">
-        <f>-('BALANCE SHEET'!K5-'BALANCE SHEET'!J5)</f>
-        <v/>
-      </c>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -5535,30 +2730,12 @@
       <c r="F22" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="G22" s="12">
-        <f>-('BALANCE SHEET'!F6-'BALANCE SHEET'!E6)</f>
-        <v/>
-      </c>
-      <c r="H22" s="12">
-        <f>-('BALANCE SHEET'!G6-'BALANCE SHEET'!F6)</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>-('BALANCE SHEET'!H6-'BALANCE SHEET'!G6)</f>
-        <v/>
-      </c>
-      <c r="J22" s="12">
-        <f>-('BALANCE SHEET'!I6-'BALANCE SHEET'!H6)</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>-('BALANCE SHEET'!J6-'BALANCE SHEET'!I6)</f>
-        <v/>
-      </c>
-      <c r="L22" s="12">
-        <f>-('BALANCE SHEET'!K6-'BALANCE SHEET'!J6)</f>
-        <v/>
-      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5581,12 +2758,12 @@
       <c r="F23" s="4" t="n">
         <v>-677</v>
       </c>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5609,12 +2786,12 @@
       <c r="F24" s="4" t="n">
         <v>-433</v>
       </c>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5637,30 +2814,12 @@
       <c r="F25" s="4" t="n">
         <v>-712</v>
       </c>
-      <c r="G25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5734,30 +2893,12 @@
       <c r="F27" s="4" t="n">
         <v>-4415</v>
       </c>
-      <c r="G27" s="12">
-        <f>'CF DRIVERS'!G5*'BALANCE SHEET'!E8</f>
-        <v/>
-      </c>
-      <c r="H27" s="12">
-        <f>'CF DRIVERS'!H5*'BALANCE SHEET'!F8</f>
-        <v/>
-      </c>
-      <c r="I27" s="12">
-        <f>'CF DRIVERS'!I5*'BALANCE SHEET'!G8</f>
-        <v/>
-      </c>
-      <c r="J27" s="12">
-        <f>'CF DRIVERS'!J5*'BALANCE SHEET'!H8</f>
-        <v/>
-      </c>
-      <c r="K27" s="12">
-        <f>'CF DRIVERS'!K5*'BALANCE SHEET'!I8</f>
-        <v/>
-      </c>
-      <c r="L27" s="12">
-        <f>'CF DRIVERS'!L5*'BALANCE SHEET'!J8</f>
-        <v/>
-      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6195,30 +3336,12 @@
       <c r="F42" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="G42" s="12">
-        <f>'CF DRIVERS'!G8</f>
-        <v/>
-      </c>
-      <c r="H42" s="12">
-        <f>'CF DRIVERS'!H8</f>
-        <v/>
-      </c>
-      <c r="I42" s="12">
-        <f>'CF DRIVERS'!I8</f>
-        <v/>
-      </c>
-      <c r="J42" s="12">
-        <f>'CF DRIVERS'!J8</f>
-        <v/>
-      </c>
-      <c r="K42" s="12">
-        <f>'CF DRIVERS'!K8</f>
-        <v/>
-      </c>
-      <c r="L42" s="12">
-        <f>'CF DRIVERS'!L8</f>
-        <v/>
-      </c>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -6241,30 +3364,12 @@
       <c r="F43" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="G43" s="12">
-        <f>F43</f>
-        <v/>
-      </c>
-      <c r="H43" s="12">
-        <f>G43</f>
-        <v/>
-      </c>
-      <c r="I43" s="12">
-        <f>H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="12">
-        <f>I43</f>
-        <v/>
-      </c>
-      <c r="K43" s="12">
-        <f>J43</f>
-        <v/>
-      </c>
-      <c r="L43" s="12">
-        <f>K43</f>
-        <v/>
-      </c>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -6394,30 +3499,12 @@
       <c r="F47" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="G47" s="12">
-        <f>F47</f>
-        <v/>
-      </c>
-      <c r="H47" s="12">
-        <f>G47</f>
-        <v/>
-      </c>
-      <c r="I47" s="12">
-        <f>H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="12">
-        <f>I47</f>
-        <v/>
-      </c>
-      <c r="K47" s="12">
-        <f>J47</f>
-        <v/>
-      </c>
-      <c r="L47" s="12">
-        <f>K47</f>
-        <v/>
-      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -6446,27 +3533,27 @@
         <v/>
       </c>
       <c r="G48" s="7">
-        <f>'CASH FLOW'!G26+'CASH FLOW'!G34+'CASH FLOW'!G46+'CASH FLOW'!G47</f>
+        <f>G26+G34+G46+G47+G48</f>
         <v/>
       </c>
       <c r="H48" s="7">
-        <f>'CASH FLOW'!H26+'CASH FLOW'!H34+'CASH FLOW'!H46+'CASH FLOW'!H47</f>
+        <f>H26+H34+H46+H47+H48</f>
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>'CASH FLOW'!I26+'CASH FLOW'!I34+'CASH FLOW'!I46+'CASH FLOW'!I47</f>
+        <f>I26+I34+I46+I47+I48</f>
         <v/>
       </c>
       <c r="J48" s="7">
-        <f>'CASH FLOW'!J26+'CASH FLOW'!J34+'CASH FLOW'!J46+'CASH FLOW'!J47</f>
+        <f>J26+J34+J46+J47+J48</f>
         <v/>
       </c>
       <c r="K48" s="7">
-        <f>'CASH FLOW'!K26+'CASH FLOW'!K34+'CASH FLOW'!K46+'CASH FLOW'!K47</f>
+        <f>K26+K34+K46+K47+K48</f>
         <v/>
       </c>
       <c r="L48" s="7">
-        <f>'CASH FLOW'!L26+'CASH FLOW'!L34+'CASH FLOW'!L46+'CASH FLOW'!L47</f>
+        <f>L26+L34+L46+L47+L48</f>
         <v/>
       </c>
     </row>
@@ -6475,1453 +3562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025E</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth %</t>
-        </is>
-      </c>
-      <c r="C2" s="13">
-        <f>IFERROR(('ANNL P&amp;L'!C2-'ANNL P&amp;L'!B2)/'ANNL P&amp;L'!B2,0)</f>
-        <v/>
-      </c>
-      <c r="D2" s="13">
-        <f>IFERROR(('ANNL P&amp;L'!D2-'ANNL P&amp;L'!C2)/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="E2" s="13">
-        <f>IFERROR(('ANNL P&amp;L'!E2-'ANNL P&amp;L'!D2)/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="F2" s="13">
-        <f>IFERROR(('ANNL P&amp;L'!F2-'ANNL P&amp;L'!E2)/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>COGS % of Revenue</t>
-        </is>
-      </c>
-      <c r="B3" s="13">
-        <f>IFERROR('ANNL P&amp;L'!B3/'ANNL P&amp;L'!B2,0)</f>
-        <v/>
-      </c>
-      <c r="C3" s="13">
-        <f>IFERROR('ANNL P&amp;L'!C3/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D3" s="13">
-        <f>IFERROR('ANNL P&amp;L'!D3/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E3" s="13">
-        <f>IFERROR('ANNL P&amp;L'!E3/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>IFERROR('ANNL P&amp;L'!F3/'ANNL P&amp;L'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="15">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="H3" s="15">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="I3" s="15">
-        <f>H3</f>
-        <v/>
-      </c>
-      <c r="J3" s="15">
-        <f>I3</f>
-        <v/>
-      </c>
-      <c r="K3" s="15">
-        <f>J3</f>
-        <v/>
-      </c>
-      <c r="L3" s="15">
-        <f>K3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A % of Revenue</t>
-        </is>
-      </c>
-      <c r="B4" s="13">
-        <f>IFERROR('ANNL P&amp;L'!B5/'ANNL P&amp;L'!B2,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>IFERROR('ANNL P&amp;L'!C5/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>IFERROR('ANNL P&amp;L'!D5/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>IFERROR('ANNL P&amp;L'!E5/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>IFERROR('ANNL P&amp;L'!F5/'ANNL P&amp;L'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="15">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="H4" s="15">
-        <f>G4</f>
-        <v/>
-      </c>
-      <c r="I4" s="15">
-        <f>H4</f>
-        <v/>
-      </c>
-      <c r="J4" s="15">
-        <f>I4</f>
-        <v/>
-      </c>
-      <c r="K4" s="15">
-        <f>J4</f>
-        <v/>
-      </c>
-      <c r="L4" s="15">
-        <f>K4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Interest Income (Expense) $</t>
-        </is>
-      </c>
-      <c r="B5" s="4">
-        <f>'ANNL P&amp;L'!B10</f>
-        <v/>
-      </c>
-      <c r="C5" s="4">
-        <f>'ANNL P&amp;L'!C10</f>
-        <v/>
-      </c>
-      <c r="D5" s="4">
-        <f>'ANNL P&amp;L'!D10</f>
-        <v/>
-      </c>
-      <c r="E5" s="4">
-        <f>'ANNL P&amp;L'!E10</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>'ANNL P&amp;L'!F10</f>
-        <v/>
-      </c>
-      <c r="G5" s="12">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="12">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="12">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="12">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Foreign Currency Gain (Loss) $</t>
-        </is>
-      </c>
-      <c r="G6" s="12">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="12">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="12">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="12">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="12">
-        <f>K6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Other Income (Expense) $</t>
-        </is>
-      </c>
-      <c r="G7" s="12">
-        <f>F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="12">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="12">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="12">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="12">
-        <f>J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="12">
-        <f>K7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate %</t>
-        </is>
-      </c>
-      <c r="G8" s="15">
-        <f>F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="15">
-        <f>G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="15">
-        <f>H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="15">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="15">
-        <f>J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="15">
-        <f>K8</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025E</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="n"/>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="17" t="n"/>
-      <c r="E2" s="17" t="n"/>
-      <c r="F2" s="17" t="n"/>
-      <c r="G2" s="17" t="n"/>
-      <c r="H2" s="17" t="n"/>
-      <c r="I2" s="17" t="n"/>
-      <c r="J2" s="17" t="n"/>
-      <c r="K2" s="17" t="n"/>
-      <c r="L2" s="17" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DSO (days)</t>
-        </is>
-      </c>
-      <c r="C3" s="18">
-        <f>IFERROR('BALANCE SHEET'!B4/'ANNL P&amp;L'!C2*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="D3" s="18">
-        <f>IFERROR('BALANCE SHEET'!C4/'ANNL P&amp;L'!D2*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="E3" s="18">
-        <f>IFERROR('BALANCE SHEET'!D4/'ANNL P&amp;L'!E2*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="F3" s="18">
-        <f>IFERROR('BALANCE SHEET'!E4/'ANNL P&amp;L'!F2*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="19">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="H3" s="19">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="I3" s="19">
-        <f>H3</f>
-        <v/>
-      </c>
-      <c r="J3" s="19">
-        <f>I3</f>
-        <v/>
-      </c>
-      <c r="K3" s="19">
-        <f>J3</f>
-        <v/>
-      </c>
-      <c r="L3" s="19">
-        <f>K3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>DIO (days)</t>
-        </is>
-      </c>
-      <c r="C4" s="18">
-        <f>IFERROR('BALANCE SHEET'!B5/'ANNL P&amp;L'!C3*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="18">
-        <f>IFERROR('BALANCE SHEET'!C5/'ANNL P&amp;L'!D3*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="18">
-        <f>IFERROR('BALANCE SHEET'!D5/'ANNL P&amp;L'!E3*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="18">
-        <f>IFERROR('BALANCE SHEET'!E5/'ANNL P&amp;L'!F3*ASSUMPTIONS!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="19">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="H4" s="19">
-        <f>G4</f>
-        <v/>
-      </c>
-      <c r="I4" s="19">
-        <f>H4</f>
-        <v/>
-      </c>
-      <c r="J4" s="19">
-        <f>I4</f>
-        <v/>
-      </c>
-      <c r="K4" s="19">
-        <f>J4</f>
-        <v/>
-      </c>
-      <c r="L4" s="19">
-        <f>K4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Note Receivable - Current % of Rev</t>
-        </is>
-      </c>
-      <c r="G5" s="15">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="15">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="15">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="15">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="15">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="15">
-        <f>K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Deferred Other Costs - Current % of Rev</t>
-        </is>
-      </c>
-      <c r="G6" s="15">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="15">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="15">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="15">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="15">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="15">
-        <f>K6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Prepaid Expenses % of Rev</t>
-        </is>
-      </c>
-      <c r="C7" s="13">
-        <f>IFERROR('BALANCE SHEET'!B6/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR('BALANCE SHEET'!C6/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR('BALANCE SHEET'!D6/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR('BALANCE SHEET'!E6/'ANNL P&amp;L'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="15">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="15">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="15">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="15">
-        <f>J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="15">
-        <f>K7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Non-Current Assets</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Other Non-Current Assets % of Rev</t>
-        </is>
-      </c>
-      <c r="C9" s="13">
-        <f>IFERROR('BALANCE SHEET'!B13/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>IFERROR('BALANCE SHEET'!C13/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="13">
-        <f>IFERROR('BALANCE SHEET'!D13/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>IFERROR('BALANCE SHEET'!E13/'ANNL P&amp;L'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="15">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="15">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="15">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="15">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="15">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="15">
-        <f>K9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="17" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DPO (days)</t>
-        </is>
-      </c>
-      <c r="G11" s="19">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="19">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="19">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="19">
-        <f>I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="19">
-        <f>J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="19">
-        <f>K11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Accrued Expenses % of Rev</t>
-        </is>
-      </c>
-      <c r="C12" s="13">
-        <f>IFERROR('BALANCE SHEET'!B16/'ANNL P&amp;L'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="13">
-        <f>IFERROR('BALANCE SHEET'!C16/'ANNL P&amp;L'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="13">
-        <f>IFERROR('BALANCE SHEET'!D16/'ANNL P&amp;L'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="13">
-        <f>IFERROR('BALANCE SHEET'!E16/'ANNL P&amp;L'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="15">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="15">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="15">
-        <f>H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="15">
-        <f>I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="15">
-        <f>J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="15">
-        <f>K12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Income Taxes Payable % of Rev</t>
-        </is>
-      </c>
-      <c r="G13" s="15">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="15">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="15">
-        <f>H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="15">
-        <f>I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="15">
-        <f>J13</f>
-        <v/>
-      </c>
-      <c r="L13" s="15">
-        <f>K13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Accrued Distributor Termination Fees % of Rev</t>
-        </is>
-      </c>
-      <c r="G14" s="15">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="15">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="15">
-        <f>H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="15">
-        <f>I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="15">
-        <f>J14</f>
-        <v/>
-      </c>
-      <c r="L14" s="15">
-        <f>K14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Accrued Promotional Allowance % of Rev</t>
-        </is>
-      </c>
-      <c r="G15" s="15">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="15">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="15">
-        <f>H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="15">
-        <f>I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="15">
-        <f>J15</f>
-        <v/>
-      </c>
-      <c r="L15" s="15">
-        <f>K15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Lease Liability - Operating - Current % of Rev</t>
-        </is>
-      </c>
-      <c r="G16" s="15">
-        <f>F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="15">
-        <f>G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="15">
-        <f>H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="15">
-        <f>I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="15">
-        <f>J16</f>
-        <v/>
-      </c>
-      <c r="L16" s="15">
-        <f>K16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Lease Liability - Finance - Current % of Rev</t>
-        </is>
-      </c>
-      <c r="G17" s="15">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="15">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="15">
-        <f>H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="15">
-        <f>I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="15">
-        <f>J17</f>
-        <v/>
-      </c>
-      <c r="L17" s="15">
-        <f>K17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Deferred Revenue - Current % of Rev</t>
-        </is>
-      </c>
-      <c r="G18" s="15">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="15">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="15">
-        <f>H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="15">
-        <f>I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="15">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="15">
-        <f>K18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities % of Rev</t>
-        </is>
-      </c>
-      <c r="G19" s="15">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="15">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="15">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="15">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="15">
-        <f>J19</f>
-        <v/>
-      </c>
-      <c r="L19" s="15">
-        <f>K19</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>FY2025E</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Allowance for Credit Losses % of Revenue</t>
-        </is>
-      </c>
-      <c r="G2" s="15">
-        <f>F2</f>
-        <v/>
-      </c>
-      <c r="H2" s="15">
-        <f>G2</f>
-        <v/>
-      </c>
-      <c r="I2" s="15">
-        <f>H2</f>
-        <v/>
-      </c>
-      <c r="J2" s="15">
-        <f>I2</f>
-        <v/>
-      </c>
-      <c r="K2" s="15">
-        <f>J2</f>
-        <v/>
-      </c>
-      <c r="L2" s="15">
-        <f>K2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A % of PP&amp;E</t>
-        </is>
-      </c>
-      <c r="D3" s="13">
-        <f>IFERROR('CASH FLOW'!D3/'BALANCE SHEET'!B8,0)</f>
-        <v/>
-      </c>
-      <c r="E3" s="13">
-        <f>IFERROR('CASH FLOW'!E3/'BALANCE SHEET'!C8,0)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>IFERROR('CASH FLOW'!F3/'BALANCE SHEET'!D8,0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="15">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="H3" s="15">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="I3" s="15">
-        <f>H3</f>
-        <v/>
-      </c>
-      <c r="J3" s="15">
-        <f>I3</f>
-        <v/>
-      </c>
-      <c r="K3" s="15">
-        <f>J3</f>
-        <v/>
-      </c>
-      <c r="L3" s="15">
-        <f>K3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SBC $</t>
-        </is>
-      </c>
-      <c r="B4" s="4">
-        <f>'CASH FLOW'!B10</f>
-        <v/>
-      </c>
-      <c r="C4" s="4">
-        <f>'CASH FLOW'!C10</f>
-        <v/>
-      </c>
-      <c r="D4" s="4">
-        <f>'CASH FLOW'!D10</f>
-        <v/>
-      </c>
-      <c r="E4" s="4">
-        <f>'CASH FLOW'!E10</f>
-        <v/>
-      </c>
-      <c r="F4" s="4">
-        <f>'CASH FLOW'!F10</f>
-        <v/>
-      </c>
-      <c r="G4" s="12">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="H4" s="12">
-        <f>G4</f>
-        <v/>
-      </c>
-      <c r="I4" s="12">
-        <f>H4</f>
-        <v/>
-      </c>
-      <c r="J4" s="12">
-        <f>I4</f>
-        <v/>
-      </c>
-      <c r="K4" s="12">
-        <f>J4</f>
-        <v/>
-      </c>
-      <c r="L4" s="12">
-        <f>K4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>CapEx % of PP&amp;E</t>
-        </is>
-      </c>
-      <c r="D5" s="13">
-        <f>IFERROR('CASH FLOW'!D27/'BALANCE SHEET'!B8,0)</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>IFERROR('CASH FLOW'!E27/'BALANCE SHEET'!C8,0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>IFERROR('CASH FLOW'!F27/'BALANCE SHEET'!D8,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="15">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="15">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="15">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="15">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="15">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="15">
-        <f>K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Preferred Dividends % of Preferred Balance</t>
-        </is>
-      </c>
-      <c r="G6" s="15">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="15">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="15">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="15">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="15">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="15">
-        <f>K6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Common Dividends % of Net Income</t>
-        </is>
-      </c>
-      <c r="B7" s="13">
-        <f>IFERROR('CASH FLOW'!B41/'CASH FLOW'!B2,0)</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>IFERROR('CASH FLOW'!C41/'CASH FLOW'!C2,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR('CASH FLOW'!D41/'CASH FLOW'!D2,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR('CASH FLOW'!E41/'CASH FLOW'!E2,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR('CASH FLOW'!F41/'CASH FLOW'!F2,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="15">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="15">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="15">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="15">
-        <f>J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="15">
-        <f>K7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Share Repurchases $</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>'CASH FLOW'!B42</f>
-        <v/>
-      </c>
-      <c r="C8" s="4">
-        <f>'CASH FLOW'!C42</f>
-        <v/>
-      </c>
-      <c r="D8" s="4">
-        <f>'CASH FLOW'!D42</f>
-        <v/>
-      </c>
-      <c r="E8" s="4">
-        <f>'CASH FLOW'!E42</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>'CASH FLOW'!F42</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-      <c r="J8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-      <c r="K8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-      <c r="L8" s="12">
-        <f>ASSUMPTIONS!$B$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Net Debt $</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8912,7 +4553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10470,4 +6111,2224 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2022</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2022</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2023</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2024</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2024</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2025</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2025</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2025</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Net Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>4273</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>5719</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>8443</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1944</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>4715</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>7831</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>2053</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>5147</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>8092</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>1843</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>3122</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>5740</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1195</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1854</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>590</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1268</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>641</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1379</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>2118</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>684</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1491</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2315</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Gain on Juice Transaction</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>-3322</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-3335</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>-3321</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Impairment and Other Charges</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>482</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1877</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1960</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Product Recall Impact</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Product Recall</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-135</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>-138</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Operating Lease ROU Asset Amortization</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>278</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>489</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Restructuring and Asset Impairment Charges</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>567</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Restructuring</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-64</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-187</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-283</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>-173</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>-284</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>-232</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>-387</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>-554</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>-145</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Acquisition and Divestiture-Related Charges</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>-113</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Acquisition and Divestiture Costs</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-41</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>-80</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Pension and Postretirement Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Pension and Postretirement Benefits Contributions</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>-178</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-214</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-335</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-175</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-209</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-374</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-218</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>-263</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>-317</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>-354</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>(Benefit) Provision for Deferred Income Taxes</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-322</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>-260</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Tax Expense Related to TCJ Act</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tax Payments Related to TCJ Act</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-309</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-309</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-309</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-309</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>-579</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>-579</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>-772</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>-772</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>-837</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-1753</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-2258</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-348</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>-1330</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-1699</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>-96</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>-1138</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>-1521</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>-318</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>-1582</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>-1747</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>-530</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>-549</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-990</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-837</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-542</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-851</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-473</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-291</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>-696</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>-492</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>-238</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>-449</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>-315</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Prepaid Expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>-190</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-186</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-124</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-288</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-242</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>-342</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>-365</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>-307</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-354</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>-223</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>-406</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>-1238</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-990</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-2259</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-1960</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-859</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>-3408</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>-2968</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>-2312</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-2671</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>-2083</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-1647</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>-1847</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>489</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>608</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>718</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>512</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Other Operating Items</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>-133</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-325</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-426</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>-203</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>-135</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>-232</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>-269</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-441</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>-157</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Operations</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>SUM(B2:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="6">
+        <f>SUM(C2:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>SUM(D2:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>SUM(E2:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>SUM(F2:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>SUM(G2:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="6">
+        <f>SUM(H2:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="6">
+        <f>SUM(I2:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="6">
+        <f>SUM(J2:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>SUM(K2:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>SUM(L2:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>SUM(M2:M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="6">
+        <f>SUM(N2:N24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Purchase of PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>-522</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-1499</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-2556</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>-581</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>-1513</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>-614</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>-1701</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>-2850</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>-603</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>-447</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Sale of Assets</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Acquisitions, Net of Cash Acquired</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-804</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>-83</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>-31</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>-3130</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-3176</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Juice Transaction</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>3456</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3456</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>3456</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Divestitures of Businesses</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Short-Term Investments</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-37</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-39</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>-421</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>441</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>278</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Other Investing Activities</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>-117</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Investing</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>SUM(B26:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>SUM(C26:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="6">
+        <f>SUM(D26:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>SUM(E26:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="6">
+        <f>SUM(F26:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="6">
+        <f>SUM(G26:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="6">
+        <f>SUM(H26:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="6">
+        <f>SUM(I26:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="6">
+        <f>SUM(J26:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="6">
+        <f>SUM(K26:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f>SUM(L26:L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>SUM(M26:M32)</f>
+        <v/>
+      </c>
+      <c r="N33" s="6">
+        <f>SUM(N26:N32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Issuance of Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>3377</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2986</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2986</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2986</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1761</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1765</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>4014</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>3505</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>3521</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>8179</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Repayments of Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>-1251</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-3202</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-3203</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>-1251</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>-2252</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-2253</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>-1252</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>-2882</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>-2883</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>-1541</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>-2543</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>-3245</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>-1629</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>559</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1947</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1660</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>4688</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>2313</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>3080</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>3808</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>3656</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>5251</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>5528</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Repayments of Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-1932</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-1037</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-1631</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>-2138</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>-4177</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>-2119</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>-2492</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>-5417</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>-676</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Other Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>647</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>844</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-45</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>491</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1395</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>774</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>1286</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>2438</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>445</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Common Dividends</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>-1505</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-2997</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-4586</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>-1608</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>-3199</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-4941</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-1767</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>-3506</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>-5369</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>-1882</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>-3743</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>-5692</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>-1966</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Share Repurchases</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>-193</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>-699</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>-453</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>-751</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>-146</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>-461</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>-760</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>-183</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>-494</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>-752</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>-182</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Exercise of Stock Options</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Tax Withholdings on RSU/PSU Settlement</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>-87</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>-97</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>-116</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-135</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>-132</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>-112</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>-76</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Other Financing Activities</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Financing</t>
+        </is>
+      </c>
+      <c r="B44" s="6">
+        <f>SUM(B34:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="6">
+        <f>SUM(C34:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="6">
+        <f>SUM(D34:D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="6">
+        <f>SUM(E34:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="6">
+        <f>SUM(F34:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="6">
+        <f>SUM(G34:G43)</f>
+        <v/>
+      </c>
+      <c r="H44" s="6">
+        <f>SUM(H34:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="6">
+        <f>SUM(I34:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="6">
+        <f>SUM(J34:J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="6">
+        <f>SUM(K34:K43)</f>
+        <v/>
+      </c>
+      <c r="L44" s="6">
+        <f>SUM(L34:L43)</f>
+        <v/>
+      </c>
+      <c r="M44" s="6">
+        <f>SUM(M34:M43)</f>
+        <v/>
+      </c>
+      <c r="N44" s="6">
+        <f>SUM(N34:N43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FX Effect on Cash</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-197</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>-116</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-254</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>-304</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>-391</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>395</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Cash</t>
+        </is>
+      </c>
+      <c r="B46" s="6">
+        <f>B25+B33+B44+B45+B46</f>
+        <v/>
+      </c>
+      <c r="C46" s="6">
+        <f>C25+C33+C44+C45+C46</f>
+        <v/>
+      </c>
+      <c r="D46" s="6">
+        <f>D25+D33+D44+D45+D46</f>
+        <v/>
+      </c>
+      <c r="E46" s="6">
+        <f>E25+E33+E44+E45+E46</f>
+        <v/>
+      </c>
+      <c r="F46" s="6">
+        <f>F25+F33+F44+F45+F46</f>
+        <v/>
+      </c>
+      <c r="G46" s="6">
+        <f>G25+G33+G44+G45+G46</f>
+        <v/>
+      </c>
+      <c r="H46" s="6">
+        <f>H25+H33+H44+H45+H46</f>
+        <v/>
+      </c>
+      <c r="I46" s="6">
+        <f>I25+I33+I44+I45+I46</f>
+        <v/>
+      </c>
+      <c r="J46" s="6">
+        <f>J25+J33+J44+J45+J46</f>
+        <v/>
+      </c>
+      <c r="K46" s="6">
+        <f>K25+K33+K44+K45+K46</f>
+        <v/>
+      </c>
+      <c r="L46" s="6">
+        <f>L25+L33+L44+L45+L46</f>
+        <v/>
+      </c>
+      <c r="M46" s="6">
+        <f>M25+M33+M44+M45+M46</f>
+        <v/>
+      </c>
+      <c r="N46" s="6">
+        <f>N25+N33+N44+N45+N46</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Knowledge/Model Schema/PEP/Model Output/PEP_model_v3.xlsx
+++ b/Knowledge/Model Schema/PEP/Model Output/PEP_model_v3.xlsx
@@ -10,9 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANNL P&amp;L" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCE SHEET" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASH FLOW" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR BS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR CF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD BS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD CF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR P&amp;L" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR BS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTR CF" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8331,4 +8334,6569 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2022</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2022</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2022</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2023</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2023</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2024</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2024</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2024</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2024</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2025</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2025</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2025</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Net Sales / Revenue</t>
+        </is>
+      </c>
+      <c r="B2" s="4">
+        <f>'YTD P&amp;L'!B2</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>'YTD P&amp;L'!C2-'YTD P&amp;L'!B2</f>
+        <v/>
+      </c>
+      <c r="D2" s="4">
+        <f>'YTD P&amp;L'!D2-'YTD P&amp;L'!C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="4">
+        <f>'ANNL P&amp;L'!C2-'YTD P&amp;L'!D2</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>'YTD P&amp;L'!E2</f>
+        <v/>
+      </c>
+      <c r="G2" s="4">
+        <f>'YTD P&amp;L'!F2-'YTD P&amp;L'!E2</f>
+        <v/>
+      </c>
+      <c r="H2" s="4">
+        <f>'YTD P&amp;L'!G2-'YTD P&amp;L'!F2</f>
+        <v/>
+      </c>
+      <c r="I2" s="4">
+        <f>'ANNL P&amp;L'!D2-'YTD P&amp;L'!G2</f>
+        <v/>
+      </c>
+      <c r="J2" s="4">
+        <f>'YTD P&amp;L'!H2</f>
+        <v/>
+      </c>
+      <c r="K2" s="4">
+        <f>'YTD P&amp;L'!I2-'YTD P&amp;L'!H2</f>
+        <v/>
+      </c>
+      <c r="L2" s="4">
+        <f>'YTD P&amp;L'!J2-'YTD P&amp;L'!I2</f>
+        <v/>
+      </c>
+      <c r="M2" s="4">
+        <f>'ANNL P&amp;L'!E2-'YTD P&amp;L'!J2</f>
+        <v/>
+      </c>
+      <c r="N2" s="4">
+        <f>'YTD P&amp;L'!K2</f>
+        <v/>
+      </c>
+      <c r="O2" s="4">
+        <f>'YTD P&amp;L'!L2-'YTD P&amp;L'!K2</f>
+        <v/>
+      </c>
+      <c r="P2" s="4">
+        <f>'YTD P&amp;L'!M2-'YTD P&amp;L'!L2</f>
+        <v/>
+      </c>
+      <c r="Q2" s="4">
+        <f>'ANNL P&amp;L'!F2-'YTD P&amp;L'!M2</f>
+        <v/>
+      </c>
+      <c r="R2" s="4">
+        <f>'YTD P&amp;L'!N2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B3" s="4">
+        <f>'YTD P&amp;L'!B3</f>
+        <v/>
+      </c>
+      <c r="C3" s="4">
+        <f>'YTD P&amp;L'!C3-'YTD P&amp;L'!B3</f>
+        <v/>
+      </c>
+      <c r="D3" s="4">
+        <f>'YTD P&amp;L'!D3-'YTD P&amp;L'!C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>'ANNL P&amp;L'!C3-'YTD P&amp;L'!D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>'YTD P&amp;L'!E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>'YTD P&amp;L'!F3-'YTD P&amp;L'!E3</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>'YTD P&amp;L'!G3-'YTD P&amp;L'!F3</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>'ANNL P&amp;L'!D3-'YTD P&amp;L'!G3</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>'YTD P&amp;L'!H3</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>'YTD P&amp;L'!I3-'YTD P&amp;L'!H3</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>'YTD P&amp;L'!J3-'YTD P&amp;L'!I3</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>'ANNL P&amp;L'!E3-'YTD P&amp;L'!J3</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>'YTD P&amp;L'!K3</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>'YTD P&amp;L'!L3-'YTD P&amp;L'!K3</f>
+        <v/>
+      </c>
+      <c r="P3" s="4">
+        <f>'YTD P&amp;L'!M3-'YTD P&amp;L'!L3</f>
+        <v/>
+      </c>
+      <c r="Q3" s="4">
+        <f>'ANNL P&amp;L'!F3-'YTD P&amp;L'!M3</f>
+        <v/>
+      </c>
+      <c r="R3" s="4">
+        <f>'YTD P&amp;L'!N3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit (Loss)</t>
+        </is>
+      </c>
+      <c r="B4" s="6">
+        <f>'YTD P&amp;L'!B4</f>
+        <v/>
+      </c>
+      <c r="C4" s="6">
+        <f>'YTD P&amp;L'!C4-'YTD P&amp;L'!B4</f>
+        <v/>
+      </c>
+      <c r="D4" s="6">
+        <f>'YTD P&amp;L'!D4-'YTD P&amp;L'!C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>'ANNL P&amp;L'!C4-'YTD P&amp;L'!D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="6">
+        <f>'YTD P&amp;L'!E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="6">
+        <f>'YTD P&amp;L'!F4-'YTD P&amp;L'!E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f>'YTD P&amp;L'!G4-'YTD P&amp;L'!F4</f>
+        <v/>
+      </c>
+      <c r="I4" s="6">
+        <f>'ANNL P&amp;L'!D4-'YTD P&amp;L'!G4</f>
+        <v/>
+      </c>
+      <c r="J4" s="6">
+        <f>'YTD P&amp;L'!H4</f>
+        <v/>
+      </c>
+      <c r="K4" s="6">
+        <f>'YTD P&amp;L'!I4-'YTD P&amp;L'!H4</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>'YTD P&amp;L'!J4-'YTD P&amp;L'!I4</f>
+        <v/>
+      </c>
+      <c r="M4" s="6">
+        <f>'ANNL P&amp;L'!E4-'YTD P&amp;L'!J4</f>
+        <v/>
+      </c>
+      <c r="N4" s="6">
+        <f>'YTD P&amp;L'!K4</f>
+        <v/>
+      </c>
+      <c r="O4" s="6">
+        <f>'YTD P&amp;L'!L4-'YTD P&amp;L'!K4</f>
+        <v/>
+      </c>
+      <c r="P4" s="6">
+        <f>'YTD P&amp;L'!M4-'YTD P&amp;L'!L4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="6">
+        <f>'ANNL P&amp;L'!F4-'YTD P&amp;L'!M4</f>
+        <v/>
+      </c>
+      <c r="R4" s="6">
+        <f>'YTD P&amp;L'!N4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>'YTD P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>'YTD P&amp;L'!C5-'YTD P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>'YTD P&amp;L'!D5-'YTD P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>'ANNL P&amp;L'!C5-'YTD P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>'YTD P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>'YTD P&amp;L'!F5-'YTD P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>'YTD P&amp;L'!G5-'YTD P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>'ANNL P&amp;L'!D5-'YTD P&amp;L'!G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>'YTD P&amp;L'!H5</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>'YTD P&amp;L'!I5-'YTD P&amp;L'!H5</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>'YTD P&amp;L'!J5-'YTD P&amp;L'!I5</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>'ANNL P&amp;L'!E5-'YTD P&amp;L'!J5</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>'YTD P&amp;L'!K5</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>'YTD P&amp;L'!L5-'YTD P&amp;L'!K5</f>
+        <v/>
+      </c>
+      <c r="P5" s="4">
+        <f>'YTD P&amp;L'!M5-'YTD P&amp;L'!L5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="4">
+        <f>'ANNL P&amp;L'!F5-'YTD P&amp;L'!M5</f>
+        <v/>
+      </c>
+      <c r="R5" s="4">
+        <f>'YTD P&amp;L'!N5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Gain on Juice Transaction</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>'YTD P&amp;L'!B6</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>'YTD P&amp;L'!C6-'YTD P&amp;L'!B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>'YTD P&amp;L'!D6-'YTD P&amp;L'!C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>'ANNL P&amp;L'!C6-'YTD P&amp;L'!D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>'YTD P&amp;L'!E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="4">
+        <f>'YTD P&amp;L'!F6-'YTD P&amp;L'!E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>'YTD P&amp;L'!G6-'YTD P&amp;L'!F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>'ANNL P&amp;L'!D6-'YTD P&amp;L'!G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>'YTD P&amp;L'!H6</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>'YTD P&amp;L'!I6-'YTD P&amp;L'!H6</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>'YTD P&amp;L'!J6-'YTD P&amp;L'!I6</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>'ANNL P&amp;L'!E6-'YTD P&amp;L'!J6</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>'YTD P&amp;L'!K6</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>'YTD P&amp;L'!L6-'YTD P&amp;L'!K6</f>
+        <v/>
+      </c>
+      <c r="P6" s="4">
+        <f>'YTD P&amp;L'!M6-'YTD P&amp;L'!L6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="4">
+        <f>'ANNL P&amp;L'!F6-'YTD P&amp;L'!M6</f>
+        <v/>
+      </c>
+      <c r="R6" s="4">
+        <f>'YTD P&amp;L'!N6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Impairment of Intangibles</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>'YTD P&amp;L'!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>'YTD P&amp;L'!C7-'YTD P&amp;L'!B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>'YTD P&amp;L'!D7-'YTD P&amp;L'!C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>'ANNL P&amp;L'!C7-'YTD P&amp;L'!D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>'YTD P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="4">
+        <f>'YTD P&amp;L'!F7-'YTD P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>'YTD P&amp;L'!G7-'YTD P&amp;L'!F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>'ANNL P&amp;L'!D7-'YTD P&amp;L'!G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>'YTD P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>'YTD P&amp;L'!I7-'YTD P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>'YTD P&amp;L'!J7-'YTD P&amp;L'!I7</f>
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <f>'ANNL P&amp;L'!E7-'YTD P&amp;L'!J7</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>'YTD P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="O7" s="4">
+        <f>'YTD P&amp;L'!L7-'YTD P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="P7" s="4">
+        <f>'YTD P&amp;L'!M7-'YTD P&amp;L'!L7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="4">
+        <f>'ANNL P&amp;L'!F7-'YTD P&amp;L'!M7</f>
+        <v/>
+      </c>
+      <c r="R7" s="4">
+        <f>'YTD P&amp;L'!N7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Income (Loss) from Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>'YTD P&amp;L'!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="6">
+        <f>'YTD P&amp;L'!C8-'YTD P&amp;L'!B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="6">
+        <f>'YTD P&amp;L'!D8-'YTD P&amp;L'!C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="6">
+        <f>'ANNL P&amp;L'!C8-'YTD P&amp;L'!D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="6">
+        <f>'YTD P&amp;L'!E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>'YTD P&amp;L'!F8-'YTD P&amp;L'!E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>'YTD P&amp;L'!G8-'YTD P&amp;L'!F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>'ANNL P&amp;L'!D8-'YTD P&amp;L'!G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="6">
+        <f>'YTD P&amp;L'!H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="6">
+        <f>'YTD P&amp;L'!I8-'YTD P&amp;L'!H8</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>'YTD P&amp;L'!J8-'YTD P&amp;L'!I8</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>'ANNL P&amp;L'!E8-'YTD P&amp;L'!J8</f>
+        <v/>
+      </c>
+      <c r="N8" s="6">
+        <f>'YTD P&amp;L'!K8</f>
+        <v/>
+      </c>
+      <c r="O8" s="6">
+        <f>'YTD P&amp;L'!L8-'YTD P&amp;L'!K8</f>
+        <v/>
+      </c>
+      <c r="P8" s="6">
+        <f>'YTD P&amp;L'!M8-'YTD P&amp;L'!L8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="6">
+        <f>'ANNL P&amp;L'!F8-'YTD P&amp;L'!M8</f>
+        <v/>
+      </c>
+      <c r="R8" s="6">
+        <f>'YTD P&amp;L'!N8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Other Pension and OPEB Benefits Income (Expense)</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>'YTD P&amp;L'!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="4">
+        <f>'YTD P&amp;L'!C9-'YTD P&amp;L'!B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="4">
+        <f>'YTD P&amp;L'!D9-'YTD P&amp;L'!C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>'ANNL P&amp;L'!C9-'YTD P&amp;L'!D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>'YTD P&amp;L'!E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>'YTD P&amp;L'!F9-'YTD P&amp;L'!E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>'YTD P&amp;L'!G9-'YTD P&amp;L'!F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>'ANNL P&amp;L'!D9-'YTD P&amp;L'!G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>'YTD P&amp;L'!H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>'YTD P&amp;L'!I9-'YTD P&amp;L'!H9</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>'YTD P&amp;L'!J9-'YTD P&amp;L'!I9</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>'ANNL P&amp;L'!E9-'YTD P&amp;L'!J9</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>'YTD P&amp;L'!K9</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>'YTD P&amp;L'!L9-'YTD P&amp;L'!K9</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>'YTD P&amp;L'!M9-'YTD P&amp;L'!L9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="4">
+        <f>'ANNL P&amp;L'!F9-'YTD P&amp;L'!M9</f>
+        <v/>
+      </c>
+      <c r="R9" s="4">
+        <f>'YTD P&amp;L'!N9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Interest Income (Expense)</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>'YTD P&amp;L'!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>'YTD P&amp;L'!C10-'YTD P&amp;L'!B10</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>'YTD P&amp;L'!D10-'YTD P&amp;L'!C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>'ANNL P&amp;L'!C10-'YTD P&amp;L'!D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>'YTD P&amp;L'!E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>'YTD P&amp;L'!F10-'YTD P&amp;L'!E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>'YTD P&amp;L'!G10-'YTD P&amp;L'!F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>'ANNL P&amp;L'!D10-'YTD P&amp;L'!G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>'YTD P&amp;L'!H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>'YTD P&amp;L'!I10-'YTD P&amp;L'!H10</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>'YTD P&amp;L'!J10-'YTD P&amp;L'!I10</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>'ANNL P&amp;L'!E10-'YTD P&amp;L'!J10</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>'YTD P&amp;L'!K10</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>'YTD P&amp;L'!L10-'YTD P&amp;L'!K10</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>'YTD P&amp;L'!M10-'YTD P&amp;L'!L10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4">
+        <f>'ANNL P&amp;L'!F10-'YTD P&amp;L'!M10</f>
+        <v/>
+      </c>
+      <c r="R10" s="4">
+        <f>'YTD P&amp;L'!N10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Tax Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <f>'YTD P&amp;L'!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="6">
+        <f>'YTD P&amp;L'!C11-'YTD P&amp;L'!B11</f>
+        <v/>
+      </c>
+      <c r="D11" s="6">
+        <f>'YTD P&amp;L'!D11-'YTD P&amp;L'!C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6">
+        <f>'ANNL P&amp;L'!C11-'YTD P&amp;L'!D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="6">
+        <f>'YTD P&amp;L'!E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>'YTD P&amp;L'!F11-'YTD P&amp;L'!E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>'YTD P&amp;L'!G11-'YTD P&amp;L'!F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>'ANNL P&amp;L'!D11-'YTD P&amp;L'!G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>'YTD P&amp;L'!H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>'YTD P&amp;L'!I11-'YTD P&amp;L'!H11</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>'YTD P&amp;L'!J11-'YTD P&amp;L'!I11</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>'ANNL P&amp;L'!E11-'YTD P&amp;L'!J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>'YTD P&amp;L'!K11</f>
+        <v/>
+      </c>
+      <c r="O11" s="6">
+        <f>'YTD P&amp;L'!L11-'YTD P&amp;L'!K11</f>
+        <v/>
+      </c>
+      <c r="P11" s="6">
+        <f>'YTD P&amp;L'!M11-'YTD P&amp;L'!L11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="6">
+        <f>'ANNL P&amp;L'!F11-'YTD P&amp;L'!M11</f>
+        <v/>
+      </c>
+      <c r="R11" s="6">
+        <f>'YTD P&amp;L'!N11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Income Tax (Expense) Benefit</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>'YTD P&amp;L'!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>'YTD P&amp;L'!C12-'YTD P&amp;L'!B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>'YTD P&amp;L'!D12-'YTD P&amp;L'!C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>'ANNL P&amp;L'!C12-'YTD P&amp;L'!D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>'YTD P&amp;L'!E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>'YTD P&amp;L'!F12-'YTD P&amp;L'!E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>'YTD P&amp;L'!G12-'YTD P&amp;L'!F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>'ANNL P&amp;L'!D12-'YTD P&amp;L'!G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>'YTD P&amp;L'!H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>'YTD P&amp;L'!I12-'YTD P&amp;L'!H12</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>'YTD P&amp;L'!J12-'YTD P&amp;L'!I12</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>'ANNL P&amp;L'!E12-'YTD P&amp;L'!J12</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>'YTD P&amp;L'!K12</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>'YTD P&amp;L'!L12-'YTD P&amp;L'!K12</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>'YTD P&amp;L'!M12-'YTD P&amp;L'!L12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="4">
+        <f>'ANNL P&amp;L'!F12-'YTD P&amp;L'!M12</f>
+        <v/>
+      </c>
+      <c r="R12" s="4">
+        <f>'YTD P&amp;L'!N12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Net Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
+        <f>'YTD P&amp;L'!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="6">
+        <f>'YTD P&amp;L'!C13-'YTD P&amp;L'!B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="6">
+        <f>'YTD P&amp;L'!D13-'YTD P&amp;L'!C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="6">
+        <f>'ANNL P&amp;L'!C13-'YTD P&amp;L'!D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="6">
+        <f>'YTD P&amp;L'!E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="6">
+        <f>'YTD P&amp;L'!F13-'YTD P&amp;L'!E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="6">
+        <f>'YTD P&amp;L'!G13-'YTD P&amp;L'!F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="6">
+        <f>'ANNL P&amp;L'!D13-'YTD P&amp;L'!G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="6">
+        <f>'YTD P&amp;L'!H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="6">
+        <f>'YTD P&amp;L'!I13-'YTD P&amp;L'!H13</f>
+        <v/>
+      </c>
+      <c r="L13" s="6">
+        <f>'YTD P&amp;L'!J13-'YTD P&amp;L'!I13</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>'ANNL P&amp;L'!E13-'YTD P&amp;L'!J13</f>
+        <v/>
+      </c>
+      <c r="N13" s="6">
+        <f>'YTD P&amp;L'!K13</f>
+        <v/>
+      </c>
+      <c r="O13" s="6">
+        <f>'YTD P&amp;L'!L13-'YTD P&amp;L'!K13</f>
+        <v/>
+      </c>
+      <c r="P13" s="6">
+        <f>'YTD P&amp;L'!M13-'YTD P&amp;L'!L13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="6">
+        <f>'ANNL P&amp;L'!F13-'YTD P&amp;L'!M13</f>
+        <v/>
+      </c>
+      <c r="R13" s="6">
+        <f>'YTD P&amp;L'!N13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Net Income (Loss) Attributable to Noncontrolling Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <f>'YTD P&amp;L'!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="4">
+        <f>'YTD P&amp;L'!C14-'YTD P&amp;L'!B14</f>
+        <v/>
+      </c>
+      <c r="D14" s="4">
+        <f>'YTD P&amp;L'!D14-'YTD P&amp;L'!C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="4">
+        <f>'ANNL P&amp;L'!C14-'YTD P&amp;L'!D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>'YTD P&amp;L'!E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>'YTD P&amp;L'!F14-'YTD P&amp;L'!E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>'YTD P&amp;L'!G14-'YTD P&amp;L'!F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>'ANNL P&amp;L'!D14-'YTD P&amp;L'!G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>'YTD P&amp;L'!H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>'YTD P&amp;L'!I14-'YTD P&amp;L'!H14</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>'YTD P&amp;L'!J14-'YTD P&amp;L'!I14</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>'ANNL P&amp;L'!E14-'YTD P&amp;L'!J14</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>'YTD P&amp;L'!K14</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>'YTD P&amp;L'!L14-'YTD P&amp;L'!K14</f>
+        <v/>
+      </c>
+      <c r="P14" s="4">
+        <f>'YTD P&amp;L'!M14-'YTD P&amp;L'!L14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="4">
+        <f>'ANNL P&amp;L'!F14-'YTD P&amp;L'!M14</f>
+        <v/>
+      </c>
+      <c r="R14" s="4">
+        <f>'YTD P&amp;L'!N14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Net Income (Loss) Less NCI</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'YTD P&amp;L'!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'YTD P&amp;L'!C15-'YTD P&amp;L'!B15</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'YTD P&amp;L'!D15-'YTD P&amp;L'!C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'ANNL P&amp;L'!C15-'YTD P&amp;L'!D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="6">
+        <f>'YTD P&amp;L'!E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="6">
+        <f>'YTD P&amp;L'!F15-'YTD P&amp;L'!E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="6">
+        <f>'YTD P&amp;L'!G15-'YTD P&amp;L'!F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="6">
+        <f>'ANNL P&amp;L'!D15-'YTD P&amp;L'!G15</f>
+        <v/>
+      </c>
+      <c r="J15" s="6">
+        <f>'YTD P&amp;L'!H15</f>
+        <v/>
+      </c>
+      <c r="K15" s="6">
+        <f>'YTD P&amp;L'!I15-'YTD P&amp;L'!H15</f>
+        <v/>
+      </c>
+      <c r="L15" s="6">
+        <f>'YTD P&amp;L'!J15-'YTD P&amp;L'!I15</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>'ANNL P&amp;L'!E15-'YTD P&amp;L'!J15</f>
+        <v/>
+      </c>
+      <c r="N15" s="6">
+        <f>'YTD P&amp;L'!K15</f>
+        <v/>
+      </c>
+      <c r="O15" s="6">
+        <f>'YTD P&amp;L'!L15-'YTD P&amp;L'!K15</f>
+        <v/>
+      </c>
+      <c r="P15" s="6">
+        <f>'YTD P&amp;L'!M15-'YTD P&amp;L'!L15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="6">
+        <f>'ANNL P&amp;L'!F15-'YTD P&amp;L'!M15</f>
+        <v/>
+      </c>
+      <c r="R15" s="6">
+        <f>'YTD P&amp;L'!N15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Basic Earnings (Loss) per Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Diluted Earnings (Loss) per Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Weighted Average Shares Outstanding (Basic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Weighted Average Shares Outstanding (Diluted)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2023</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2023</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2024</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2024</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2024</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2025</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2025</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2025</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2025</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B2" s="4">
+        <f>'BALANCE SHEET'!B2</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>'YTD BS'!C2</f>
+        <v/>
+      </c>
+      <c r="D2" s="4">
+        <f>'YTD BS'!D2</f>
+        <v/>
+      </c>
+      <c r="E2" s="4">
+        <f>'YTD BS'!E2</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>'BALANCE SHEET'!C2</f>
+        <v/>
+      </c>
+      <c r="G2" s="4">
+        <f>'YTD BS'!G2</f>
+        <v/>
+      </c>
+      <c r="H2" s="4">
+        <f>'YTD BS'!H2</f>
+        <v/>
+      </c>
+      <c r="I2" s="4">
+        <f>'YTD BS'!I2</f>
+        <v/>
+      </c>
+      <c r="J2" s="4">
+        <f>'BALANCE SHEET'!D2</f>
+        <v/>
+      </c>
+      <c r="K2" s="4">
+        <f>'YTD BS'!K2</f>
+        <v/>
+      </c>
+      <c r="L2" s="4">
+        <f>'YTD BS'!L2</f>
+        <v/>
+      </c>
+      <c r="M2" s="4">
+        <f>'YTD BS'!M2</f>
+        <v/>
+      </c>
+      <c r="N2" s="4">
+        <f>'BALANCE SHEET'!E2</f>
+        <v/>
+      </c>
+      <c r="O2" s="4">
+        <f>'YTD BS'!O2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Short-Term Investments</t>
+        </is>
+      </c>
+      <c r="B3" s="4">
+        <f>'BALANCE SHEET'!B3</f>
+        <v/>
+      </c>
+      <c r="C3" s="4">
+        <f>'YTD BS'!C3</f>
+        <v/>
+      </c>
+      <c r="D3" s="4">
+        <f>'YTD BS'!D3</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>'YTD BS'!E3</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>'BALANCE SHEET'!C3</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>'YTD BS'!G3</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>'YTD BS'!H3</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>'YTD BS'!I3</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>'BALANCE SHEET'!D3</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>'YTD BS'!K3</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>'YTD BS'!L3</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>'YTD BS'!M3</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>'BALANCE SHEET'!E3</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>'YTD BS'!O3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>'BALANCE SHEET'!B4</f>
+        <v/>
+      </c>
+      <c r="C4" s="4">
+        <f>'YTD BS'!C4</f>
+        <v/>
+      </c>
+      <c r="D4" s="4">
+        <f>'YTD BS'!D4</f>
+        <v/>
+      </c>
+      <c r="E4" s="4">
+        <f>'YTD BS'!E4</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>'BALANCE SHEET'!C4</f>
+        <v/>
+      </c>
+      <c r="G4" s="4">
+        <f>'YTD BS'!G4</f>
+        <v/>
+      </c>
+      <c r="H4" s="4">
+        <f>'YTD BS'!H4</f>
+        <v/>
+      </c>
+      <c r="I4" s="4">
+        <f>'YTD BS'!I4</f>
+        <v/>
+      </c>
+      <c r="J4" s="4">
+        <f>'BALANCE SHEET'!D4</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>'YTD BS'!K4</f>
+        <v/>
+      </c>
+      <c r="L4" s="4">
+        <f>'YTD BS'!L4</f>
+        <v/>
+      </c>
+      <c r="M4" s="4">
+        <f>'YTD BS'!M4</f>
+        <v/>
+      </c>
+      <c r="N4" s="4">
+        <f>'BALANCE SHEET'!E4</f>
+        <v/>
+      </c>
+      <c r="O4" s="4">
+        <f>'YTD BS'!O4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>'BALANCE SHEET'!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>'YTD BS'!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>'YTD BS'!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>'YTD BS'!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>'BALANCE SHEET'!C5</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>'YTD BS'!G5</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>'YTD BS'!H5</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>'YTD BS'!I5</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>'BALANCE SHEET'!D5</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>'YTD BS'!K5</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>'YTD BS'!L5</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>'YTD BS'!M5</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>'BALANCE SHEET'!E5</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>'YTD BS'!O5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Prepaid Expenses</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>'BALANCE SHEET'!B6</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>'YTD BS'!C6</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>'YTD BS'!D6</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>'YTD BS'!E6</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>'BALANCE SHEET'!C6</f>
+        <v/>
+      </c>
+      <c r="G6" s="4">
+        <f>'YTD BS'!G6</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>'YTD BS'!H6</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>'YTD BS'!I6</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>'BALANCE SHEET'!D6</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>'YTD BS'!K6</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>'YTD BS'!L6</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>'YTD BS'!M6</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>'BALANCE SHEET'!E6</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>'YTD BS'!O6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>'BALANCE SHEET'!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="6">
+        <f>'YTD BS'!C7</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
+        <f>'YTD BS'!D7</f>
+        <v/>
+      </c>
+      <c r="E7" s="6">
+        <f>'YTD BS'!E7</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>'BALANCE SHEET'!C7</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
+        <f>'YTD BS'!G7</f>
+        <v/>
+      </c>
+      <c r="H7" s="6">
+        <f>'YTD BS'!H7</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>'YTD BS'!I7</f>
+        <v/>
+      </c>
+      <c r="J7" s="6">
+        <f>'BALANCE SHEET'!D7</f>
+        <v/>
+      </c>
+      <c r="K7" s="6">
+        <f>'YTD BS'!K7</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>'YTD BS'!L7</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>'YTD BS'!M7</f>
+        <v/>
+      </c>
+      <c r="N7" s="6">
+        <f>'BALANCE SHEET'!E7</f>
+        <v/>
+      </c>
+      <c r="O7" s="6">
+        <f>'YTD BS'!O7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>'BALANCE SHEET'!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="4">
+        <f>'YTD BS'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="4">
+        <f>'YTD BS'!D8</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>'YTD BS'!E8</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>'BALANCE SHEET'!C8</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>'YTD BS'!G8</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>'YTD BS'!H8</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>'YTD BS'!I8</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>'BALANCE SHEET'!D8</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>'YTD BS'!K8</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>'YTD BS'!L8</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>'YTD BS'!M8</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>'BALANCE SHEET'!E8</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>'YTD BS'!O8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>'BALANCE SHEET'!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="4">
+        <f>'YTD BS'!C9</f>
+        <v/>
+      </c>
+      <c r="D9" s="4">
+        <f>'YTD BS'!D9</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>'YTD BS'!E9</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>'BALANCE SHEET'!C9</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>'YTD BS'!G9</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>'YTD BS'!H9</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>'YTD BS'!I9</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>'BALANCE SHEET'!D9</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>'YTD BS'!K9</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>'YTD BS'!L9</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>'YTD BS'!M9</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>'BALANCE SHEET'!E9</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>'YTD BS'!O9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>'BALANCE SHEET'!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>'YTD BS'!C10</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>'YTD BS'!D10</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>'YTD BS'!E10</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>'BALANCE SHEET'!C10</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>'YTD BS'!G10</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>'YTD BS'!H10</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>'YTD BS'!I10</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>'BALANCE SHEET'!D10</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>'YTD BS'!K10</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>'YTD BS'!L10</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>'YTD BS'!M10</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>'BALANCE SHEET'!E10</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>'YTD BS'!O10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Equity Method Investments</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>'BALANCE SHEET'!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="4">
+        <f>'YTD BS'!C11</f>
+        <v/>
+      </c>
+      <c r="D11" s="4">
+        <f>'YTD BS'!D11</f>
+        <v/>
+      </c>
+      <c r="E11" s="4">
+        <f>'YTD BS'!E11</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>'BALANCE SHEET'!C11</f>
+        <v/>
+      </c>
+      <c r="G11" s="4">
+        <f>'YTD BS'!G11</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>'YTD BS'!H11</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>'YTD BS'!I11</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>'BALANCE SHEET'!D11</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>'YTD BS'!K11</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>'YTD BS'!L11</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>'YTD BS'!M11</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>'BALANCE SHEET'!E11</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>'YTD BS'!O11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>'BALANCE SHEET'!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>'YTD BS'!C12</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>'YTD BS'!D12</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>'YTD BS'!E12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>'BALANCE SHEET'!C12</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>'YTD BS'!G12</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>'YTD BS'!H12</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>'YTD BS'!I12</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>'BALANCE SHEET'!D12</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>'YTD BS'!K12</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>'YTD BS'!L12</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>'YTD BS'!M12</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>'BALANCE SHEET'!E12</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>'YTD BS'!O12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Other Non-Current Assets</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <f>'BALANCE SHEET'!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="4">
+        <f>'YTD BS'!C13</f>
+        <v/>
+      </c>
+      <c r="D13" s="4">
+        <f>'YTD BS'!D13</f>
+        <v/>
+      </c>
+      <c r="E13" s="4">
+        <f>'YTD BS'!E13</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>'BALANCE SHEET'!C13</f>
+        <v/>
+      </c>
+      <c r="G13" s="4">
+        <f>'YTD BS'!G13</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>'YTD BS'!H13</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>'YTD BS'!I13</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>'BALANCE SHEET'!D13</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>'YTD BS'!K13</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>'YTD BS'!L13</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>'YTD BS'!M13</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>'BALANCE SHEET'!E13</f>
+        <v/>
+      </c>
+      <c r="O13" s="4">
+        <f>'YTD BS'!O13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>'BALANCE SHEET'!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="6">
+        <f>'YTD BS'!C14</f>
+        <v/>
+      </c>
+      <c r="D14" s="6">
+        <f>'YTD BS'!D14</f>
+        <v/>
+      </c>
+      <c r="E14" s="6">
+        <f>'YTD BS'!E14</f>
+        <v/>
+      </c>
+      <c r="F14" s="6">
+        <f>'BALANCE SHEET'!C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="6">
+        <f>'YTD BS'!G14</f>
+        <v/>
+      </c>
+      <c r="H14" s="6">
+        <f>'YTD BS'!H14</f>
+        <v/>
+      </c>
+      <c r="I14" s="6">
+        <f>'YTD BS'!I14</f>
+        <v/>
+      </c>
+      <c r="J14" s="6">
+        <f>'BALANCE SHEET'!D14</f>
+        <v/>
+      </c>
+      <c r="K14" s="6">
+        <f>'YTD BS'!K14</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>'YTD BS'!L14</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>'YTD BS'!M14</f>
+        <v/>
+      </c>
+      <c r="N14" s="6">
+        <f>'BALANCE SHEET'!E14</f>
+        <v/>
+      </c>
+      <c r="O14" s="6">
+        <f>'YTD BS'!O14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Short-Term Debt Obligations</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>'BALANCE SHEET'!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="4">
+        <f>'YTD BS'!C15</f>
+        <v/>
+      </c>
+      <c r="D15" s="4">
+        <f>'YTD BS'!D15</f>
+        <v/>
+      </c>
+      <c r="E15" s="4">
+        <f>'YTD BS'!E15</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>'BALANCE SHEET'!C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>'YTD BS'!G15</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>'YTD BS'!H15</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>'YTD BS'!I15</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>'BALANCE SHEET'!D15</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>'YTD BS'!K15</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>'YTD BS'!L15</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>'YTD BS'!M15</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>'BALANCE SHEET'!E15</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>'YTD BS'!O15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>'BALANCE SHEET'!B16</f>
+        <v/>
+      </c>
+      <c r="C16" s="4">
+        <f>'YTD BS'!C16</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>'YTD BS'!D16</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>'YTD BS'!E16</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>'BALANCE SHEET'!C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>'YTD BS'!G16</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>'YTD BS'!H16</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>'YTD BS'!I16</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>'BALANCE SHEET'!D16</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>'YTD BS'!K16</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>'YTD BS'!L16</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>'YTD BS'!M16</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>'BALANCE SHEET'!E16</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>'YTD BS'!O16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>'BALANCE SHEET'!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="6">
+        <f>'YTD BS'!C17</f>
+        <v/>
+      </c>
+      <c r="D17" s="6">
+        <f>'YTD BS'!D17</f>
+        <v/>
+      </c>
+      <c r="E17" s="6">
+        <f>'YTD BS'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="6">
+        <f>'BALANCE SHEET'!C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="6">
+        <f>'YTD BS'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="6">
+        <f>'YTD BS'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="6">
+        <f>'YTD BS'!I17</f>
+        <v/>
+      </c>
+      <c r="J17" s="6">
+        <f>'BALANCE SHEET'!D17</f>
+        <v/>
+      </c>
+      <c r="K17" s="6">
+        <f>'YTD BS'!K17</f>
+        <v/>
+      </c>
+      <c r="L17" s="6">
+        <f>'YTD BS'!L17</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>'YTD BS'!M17</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>'BALANCE SHEET'!E17</f>
+        <v/>
+      </c>
+      <c r="O17" s="6">
+        <f>'YTD BS'!O17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <f>'BALANCE SHEET'!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="4">
+        <f>'YTD BS'!C18</f>
+        <v/>
+      </c>
+      <c r="D18" s="4">
+        <f>'YTD BS'!D18</f>
+        <v/>
+      </c>
+      <c r="E18" s="4">
+        <f>'YTD BS'!E18</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>'BALANCE SHEET'!C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>'YTD BS'!G18</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>'YTD BS'!H18</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>'YTD BS'!I18</f>
+        <v/>
+      </c>
+      <c r="J18" s="4">
+        <f>'BALANCE SHEET'!D18</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>'YTD BS'!K18</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>'YTD BS'!L18</f>
+        <v/>
+      </c>
+      <c r="M18" s="4">
+        <f>'YTD BS'!M18</f>
+        <v/>
+      </c>
+      <c r="N18" s="4">
+        <f>'BALANCE SHEET'!E18</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>'YTD BS'!O18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liability</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>'BALANCE SHEET'!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="4">
+        <f>'YTD BS'!C19</f>
+        <v/>
+      </c>
+      <c r="D19" s="4">
+        <f>'YTD BS'!D19</f>
+        <v/>
+      </c>
+      <c r="E19" s="4">
+        <f>'YTD BS'!E19</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>'BALANCE SHEET'!C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>'YTD BS'!G19</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>'YTD BS'!H19</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>'YTD BS'!I19</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>'BALANCE SHEET'!D19</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>'YTD BS'!K19</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>'YTD BS'!L19</f>
+        <v/>
+      </c>
+      <c r="M19" s="4">
+        <f>'YTD BS'!M19</f>
+        <v/>
+      </c>
+      <c r="N19" s="4">
+        <f>'BALANCE SHEET'!E19</f>
+        <v/>
+      </c>
+      <c r="O19" s="4">
+        <f>'YTD BS'!O19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Other Non-Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <f>'BALANCE SHEET'!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="4">
+        <f>'YTD BS'!C20</f>
+        <v/>
+      </c>
+      <c r="D20" s="4">
+        <f>'YTD BS'!D20</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>'YTD BS'!E20</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>'BALANCE SHEET'!C20</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>'YTD BS'!G20</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>'YTD BS'!H20</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>'YTD BS'!I20</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>'BALANCE SHEET'!D20</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>'YTD BS'!K20</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>'YTD BS'!L20</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>'YTD BS'!M20</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>'BALANCE SHEET'!E20</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>'YTD BS'!O20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>'BALANCE SHEET'!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="6">
+        <f>'YTD BS'!C21</f>
+        <v/>
+      </c>
+      <c r="D21" s="6">
+        <f>'YTD BS'!D21</f>
+        <v/>
+      </c>
+      <c r="E21" s="6">
+        <f>'YTD BS'!E21</f>
+        <v/>
+      </c>
+      <c r="F21" s="6">
+        <f>'BALANCE SHEET'!C21</f>
+        <v/>
+      </c>
+      <c r="G21" s="6">
+        <f>'YTD BS'!G21</f>
+        <v/>
+      </c>
+      <c r="H21" s="6">
+        <f>'YTD BS'!H21</f>
+        <v/>
+      </c>
+      <c r="I21" s="6">
+        <f>'YTD BS'!I21</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>'BALANCE SHEET'!D21</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>'YTD BS'!K21</f>
+        <v/>
+      </c>
+      <c r="L21" s="6">
+        <f>'YTD BS'!L21</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>'YTD BS'!M21</f>
+        <v/>
+      </c>
+      <c r="N21" s="6">
+        <f>'BALANCE SHEET'!E21</f>
+        <v/>
+      </c>
+      <c r="O21" s="6">
+        <f>'YTD BS'!O21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="4">
+        <f>'BALANCE SHEET'!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="4">
+        <f>'YTD BS'!C22</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>'YTD BS'!D22</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>'YTD BS'!E22</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>'BALANCE SHEET'!C22</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>'YTD BS'!G22</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>'YTD BS'!H22</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>'YTD BS'!I22</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>'BALANCE SHEET'!D22</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>'YTD BS'!K22</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>'YTD BS'!L22</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>'YTD BS'!M22</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>'BALANCE SHEET'!E22</f>
+        <v/>
+      </c>
+      <c r="O22" s="4">
+        <f>'YTD BS'!O22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Additional Paid-in Capital</t>
+        </is>
+      </c>
+      <c r="B23" s="4">
+        <f>'BALANCE SHEET'!B23</f>
+        <v/>
+      </c>
+      <c r="C23" s="4">
+        <f>'YTD BS'!C23</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>'YTD BS'!D23</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>'YTD BS'!E23</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>'BALANCE SHEET'!C23</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>'YTD BS'!G23</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>'YTD BS'!H23</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>'YTD BS'!I23</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>'BALANCE SHEET'!D23</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>'YTD BS'!K23</f>
+        <v/>
+      </c>
+      <c r="L23" s="4">
+        <f>'YTD BS'!L23</f>
+        <v/>
+      </c>
+      <c r="M23" s="4">
+        <f>'YTD BS'!M23</f>
+        <v/>
+      </c>
+      <c r="N23" s="4">
+        <f>'BALANCE SHEET'!E23</f>
+        <v/>
+      </c>
+      <c r="O23" s="4">
+        <f>'YTD BS'!O23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Retained Earnings (Accumulated Deficit)</t>
+        </is>
+      </c>
+      <c r="B24" s="4">
+        <f>'BALANCE SHEET'!B24</f>
+        <v/>
+      </c>
+      <c r="C24" s="4">
+        <f>'YTD BS'!C24</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f>'YTD BS'!D24</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>'YTD BS'!E24</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>'BALANCE SHEET'!C24</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>'YTD BS'!G24</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>'YTD BS'!H24</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>'YTD BS'!I24</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>'BALANCE SHEET'!D24</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>'YTD BS'!K24</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>'YTD BS'!L24</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>'YTD BS'!M24</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>'BALANCE SHEET'!E24</f>
+        <v/>
+      </c>
+      <c r="O24" s="4">
+        <f>'YTD BS'!O24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Accumulated Other Comprehensive Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B25" s="4">
+        <f>'BALANCE SHEET'!B25</f>
+        <v/>
+      </c>
+      <c r="C25" s="4">
+        <f>'YTD BS'!C25</f>
+        <v/>
+      </c>
+      <c r="D25" s="4">
+        <f>'YTD BS'!D25</f>
+        <v/>
+      </c>
+      <c r="E25" s="4">
+        <f>'YTD BS'!E25</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>'BALANCE SHEET'!C25</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>'YTD BS'!G25</f>
+        <v/>
+      </c>
+      <c r="H25" s="4">
+        <f>'YTD BS'!H25</f>
+        <v/>
+      </c>
+      <c r="I25" s="4">
+        <f>'YTD BS'!I25</f>
+        <v/>
+      </c>
+      <c r="J25" s="4">
+        <f>'BALANCE SHEET'!D25</f>
+        <v/>
+      </c>
+      <c r="K25" s="4">
+        <f>'YTD BS'!K25</f>
+        <v/>
+      </c>
+      <c r="L25" s="4">
+        <f>'YTD BS'!L25</f>
+        <v/>
+      </c>
+      <c r="M25" s="4">
+        <f>'YTD BS'!M25</f>
+        <v/>
+      </c>
+      <c r="N25" s="4">
+        <f>'BALANCE SHEET'!E25</f>
+        <v/>
+      </c>
+      <c r="O25" s="4">
+        <f>'YTD BS'!O25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <f>'BALANCE SHEET'!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="4">
+        <f>'YTD BS'!C26</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>'YTD BS'!D26</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>'YTD BS'!E26</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>'BALANCE SHEET'!C26</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>'YTD BS'!G26</f>
+        <v/>
+      </c>
+      <c r="H26" s="4">
+        <f>'YTD BS'!H26</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>'YTD BS'!I26</f>
+        <v/>
+      </c>
+      <c r="J26" s="4">
+        <f>'BALANCE SHEET'!D26</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>'YTD BS'!K26</f>
+        <v/>
+      </c>
+      <c r="L26" s="4">
+        <f>'YTD BS'!L26</f>
+        <v/>
+      </c>
+      <c r="M26" s="4">
+        <f>'YTD BS'!M26</f>
+        <v/>
+      </c>
+      <c r="N26" s="4">
+        <f>'BALANCE SHEET'!E26</f>
+        <v/>
+      </c>
+      <c r="O26" s="4">
+        <f>'YTD BS'!O26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Noncontrolling Interest</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>'BALANCE SHEET'!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="4">
+        <f>'YTD BS'!C27</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>'YTD BS'!D27</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f>'YTD BS'!E27</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>'BALANCE SHEET'!C27</f>
+        <v/>
+      </c>
+      <c r="G27" s="4">
+        <f>'YTD BS'!G27</f>
+        <v/>
+      </c>
+      <c r="H27" s="4">
+        <f>'YTD BS'!H27</f>
+        <v/>
+      </c>
+      <c r="I27" s="4">
+        <f>'YTD BS'!I27</f>
+        <v/>
+      </c>
+      <c r="J27" s="4">
+        <f>'BALANCE SHEET'!D27</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>'YTD BS'!K27</f>
+        <v/>
+      </c>
+      <c r="L27" s="4">
+        <f>'YTD BS'!L27</f>
+        <v/>
+      </c>
+      <c r="M27" s="4">
+        <f>'YTD BS'!M27</f>
+        <v/>
+      </c>
+      <c r="N27" s="4">
+        <f>'BALANCE SHEET'!E27</f>
+        <v/>
+      </c>
+      <c r="O27" s="4">
+        <f>'YTD BS'!O27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Total Stockholders' Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>'BALANCE SHEET'!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="6">
+        <f>'YTD BS'!C28</f>
+        <v/>
+      </c>
+      <c r="D28" s="6">
+        <f>'YTD BS'!D28</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
+        <f>'YTD BS'!E28</f>
+        <v/>
+      </c>
+      <c r="F28" s="6">
+        <f>'BALANCE SHEET'!C28</f>
+        <v/>
+      </c>
+      <c r="G28" s="6">
+        <f>'YTD BS'!G28</f>
+        <v/>
+      </c>
+      <c r="H28" s="6">
+        <f>'YTD BS'!H28</f>
+        <v/>
+      </c>
+      <c r="I28" s="6">
+        <f>'YTD BS'!I28</f>
+        <v/>
+      </c>
+      <c r="J28" s="6">
+        <f>'BALANCE SHEET'!D28</f>
+        <v/>
+      </c>
+      <c r="K28" s="6">
+        <f>'YTD BS'!K28</f>
+        <v/>
+      </c>
+      <c r="L28" s="6">
+        <f>'YTD BS'!L28</f>
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <f>'YTD BS'!M28</f>
+        <v/>
+      </c>
+      <c r="N28" s="6">
+        <f>'BALANCE SHEET'!E28</f>
+        <v/>
+      </c>
+      <c r="O28" s="6">
+        <f>'YTD BS'!O28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Total Liabilities, Mezzanine &amp; Stockholders' Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>'BALANCE SHEET'!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="6">
+        <f>'YTD BS'!C29</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>'YTD BS'!D29</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
+        <f>'YTD BS'!E29</f>
+        <v/>
+      </c>
+      <c r="F29" s="6">
+        <f>'BALANCE SHEET'!C29</f>
+        <v/>
+      </c>
+      <c r="G29" s="6">
+        <f>'YTD BS'!G29</f>
+        <v/>
+      </c>
+      <c r="H29" s="6">
+        <f>'YTD BS'!H29</f>
+        <v/>
+      </c>
+      <c r="I29" s="6">
+        <f>'YTD BS'!I29</f>
+        <v/>
+      </c>
+      <c r="J29" s="6">
+        <f>'BALANCE SHEET'!D29</f>
+        <v/>
+      </c>
+      <c r="K29" s="6">
+        <f>'YTD BS'!K29</f>
+        <v/>
+      </c>
+      <c r="L29" s="6">
+        <f>'YTD BS'!L29</f>
+        <v/>
+      </c>
+      <c r="M29" s="6">
+        <f>'YTD BS'!M29</f>
+        <v/>
+      </c>
+      <c r="N29" s="6">
+        <f>'BALANCE SHEET'!E29</f>
+        <v/>
+      </c>
+      <c r="O29" s="6">
+        <f>'YTD BS'!O29</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2022</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2022</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2022</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2023</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2023</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2024</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2024</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2024</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2024</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2025</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY2025</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY2025</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Net Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B2" s="4">
+        <f>'YTD CF'!B2</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>'YTD CF'!C2-'YTD CF'!B2</f>
+        <v/>
+      </c>
+      <c r="D2" s="4">
+        <f>'YTD CF'!D2-'YTD CF'!C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="4">
+        <f>'CASH FLOW'!C2-'YTD CF'!D2</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>'YTD CF'!E2</f>
+        <v/>
+      </c>
+      <c r="G2" s="4">
+        <f>'YTD CF'!F2-'YTD CF'!E2</f>
+        <v/>
+      </c>
+      <c r="H2" s="4">
+        <f>'YTD CF'!G2-'YTD CF'!F2</f>
+        <v/>
+      </c>
+      <c r="I2" s="4">
+        <f>'CASH FLOW'!D2-'YTD CF'!G2</f>
+        <v/>
+      </c>
+      <c r="J2" s="4">
+        <f>'YTD CF'!H2</f>
+        <v/>
+      </c>
+      <c r="K2" s="4">
+        <f>'YTD CF'!I2-'YTD CF'!H2</f>
+        <v/>
+      </c>
+      <c r="L2" s="4">
+        <f>'YTD CF'!J2-'YTD CF'!I2</f>
+        <v/>
+      </c>
+      <c r="M2" s="4">
+        <f>'CASH FLOW'!E2-'YTD CF'!J2</f>
+        <v/>
+      </c>
+      <c r="N2" s="4">
+        <f>'YTD CF'!K2</f>
+        <v/>
+      </c>
+      <c r="O2" s="4">
+        <f>'YTD CF'!L2-'YTD CF'!K2</f>
+        <v/>
+      </c>
+      <c r="P2" s="4">
+        <f>'YTD CF'!M2-'YTD CF'!L2</f>
+        <v/>
+      </c>
+      <c r="Q2" s="4">
+        <f>'CASH FLOW'!F2-'YTD CF'!M2</f>
+        <v/>
+      </c>
+      <c r="R2" s="4">
+        <f>'YTD CF'!N2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B3" s="4">
+        <f>'YTD CF'!B3</f>
+        <v/>
+      </c>
+      <c r="C3" s="4">
+        <f>'YTD CF'!C3-'YTD CF'!B3</f>
+        <v/>
+      </c>
+      <c r="D3" s="4">
+        <f>'YTD CF'!D3-'YTD CF'!C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>'CASH FLOW'!C3-'YTD CF'!D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>'YTD CF'!E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>'YTD CF'!F3-'YTD CF'!E3</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>'YTD CF'!G3-'YTD CF'!F3</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>'CASH FLOW'!D3-'YTD CF'!G3</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>'YTD CF'!H3</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>'YTD CF'!I3-'YTD CF'!H3</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>'YTD CF'!J3-'YTD CF'!I3</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>'CASH FLOW'!E3-'YTD CF'!J3</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>'YTD CF'!K3</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>'YTD CF'!L3-'YTD CF'!K3</f>
+        <v/>
+      </c>
+      <c r="P3" s="4">
+        <f>'YTD CF'!M3-'YTD CF'!L3</f>
+        <v/>
+      </c>
+      <c r="Q3" s="4">
+        <f>'CASH FLOW'!F3-'YTD CF'!M3</f>
+        <v/>
+      </c>
+      <c r="R3" s="4">
+        <f>'YTD CF'!N3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Gain on Juice Transaction</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>'YTD CF'!B4</f>
+        <v/>
+      </c>
+      <c r="C4" s="4">
+        <f>'YTD CF'!C4-'YTD CF'!B4</f>
+        <v/>
+      </c>
+      <c r="D4" s="4">
+        <f>'YTD CF'!D4-'YTD CF'!C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="4">
+        <f>'CASH FLOW'!C4-'YTD CF'!D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>'YTD CF'!E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="4">
+        <f>'YTD CF'!F4-'YTD CF'!E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="4">
+        <f>'YTD CF'!G4-'YTD CF'!F4</f>
+        <v/>
+      </c>
+      <c r="I4" s="4">
+        <f>'CASH FLOW'!D4-'YTD CF'!G4</f>
+        <v/>
+      </c>
+      <c r="J4" s="4">
+        <f>'YTD CF'!H4</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>'YTD CF'!I4-'YTD CF'!H4</f>
+        <v/>
+      </c>
+      <c r="L4" s="4">
+        <f>'YTD CF'!J4-'YTD CF'!I4</f>
+        <v/>
+      </c>
+      <c r="M4" s="4">
+        <f>'CASH FLOW'!E4-'YTD CF'!J4</f>
+        <v/>
+      </c>
+      <c r="N4" s="4">
+        <f>'YTD CF'!K4</f>
+        <v/>
+      </c>
+      <c r="O4" s="4">
+        <f>'YTD CF'!L4-'YTD CF'!K4</f>
+        <v/>
+      </c>
+      <c r="P4" s="4">
+        <f>'YTD CF'!M4-'YTD CF'!L4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="4">
+        <f>'CASH FLOW'!F4-'YTD CF'!M4</f>
+        <v/>
+      </c>
+      <c r="R4" s="4">
+        <f>'YTD CF'!N4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Impairment and Other Charges</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>'YTD CF'!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>'YTD CF'!C5-'YTD CF'!B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>'YTD CF'!D5-'YTD CF'!C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>'CASH FLOW'!C5-'YTD CF'!D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>'YTD CF'!E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>'YTD CF'!F5-'YTD CF'!E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>'YTD CF'!G5-'YTD CF'!F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>'CASH FLOW'!D5-'YTD CF'!G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>'YTD CF'!H5</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>'YTD CF'!I5-'YTD CF'!H5</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>'YTD CF'!J5-'YTD CF'!I5</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>'CASH FLOW'!E5-'YTD CF'!J5</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>'YTD CF'!K5</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>'YTD CF'!L5-'YTD CF'!K5</f>
+        <v/>
+      </c>
+      <c r="P5" s="4">
+        <f>'YTD CF'!M5-'YTD CF'!L5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="4">
+        <f>'CASH FLOW'!F5-'YTD CF'!M5</f>
+        <v/>
+      </c>
+      <c r="R5" s="4">
+        <f>'YTD CF'!N5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Product Recall Impact</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>'YTD CF'!B6</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>'YTD CF'!C6-'YTD CF'!B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>'YTD CF'!D6-'YTD CF'!C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>'CASH FLOW'!C7-'YTD CF'!D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>'YTD CF'!E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="4">
+        <f>'YTD CF'!F6-'YTD CF'!E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>'YTD CF'!G6-'YTD CF'!F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>'CASH FLOW'!D7-'YTD CF'!G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>'YTD CF'!H6</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>'YTD CF'!I6-'YTD CF'!H6</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>'YTD CF'!J6-'YTD CF'!I6</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>'CASH FLOW'!E7-'YTD CF'!J6</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>'YTD CF'!K6</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>'YTD CF'!L6-'YTD CF'!K6</f>
+        <v/>
+      </c>
+      <c r="P6" s="4">
+        <f>'YTD CF'!M6-'YTD CF'!L6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="4">
+        <f>'CASH FLOW'!F7-'YTD CF'!M6</f>
+        <v/>
+      </c>
+      <c r="R6" s="4">
+        <f>'YTD CF'!N6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Product Recall</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>'YTD CF'!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>'YTD CF'!C7-'YTD CF'!B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>'YTD CF'!D7-'YTD CF'!C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>'CASH FLOW'!C8-'YTD CF'!D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>'YTD CF'!E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="4">
+        <f>'YTD CF'!F7-'YTD CF'!E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>'YTD CF'!G7-'YTD CF'!F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>'CASH FLOW'!D8-'YTD CF'!G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>'YTD CF'!H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>'YTD CF'!I7-'YTD CF'!H7</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>'YTD CF'!J7-'YTD CF'!I7</f>
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <f>'CASH FLOW'!E8-'YTD CF'!J7</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>'YTD CF'!K7</f>
+        <v/>
+      </c>
+      <c r="O7" s="4">
+        <f>'YTD CF'!L7-'YTD CF'!K7</f>
+        <v/>
+      </c>
+      <c r="P7" s="4">
+        <f>'YTD CF'!M7-'YTD CF'!L7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="4">
+        <f>'CASH FLOW'!F8-'YTD CF'!M7</f>
+        <v/>
+      </c>
+      <c r="R7" s="4">
+        <f>'YTD CF'!N7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Operating Lease ROU Asset Amortization</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>'YTD CF'!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="4">
+        <f>'YTD CF'!C8-'YTD CF'!B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="4">
+        <f>'YTD CF'!D8-'YTD CF'!C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>'CASH FLOW'!C9-'YTD CF'!D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>'YTD CF'!E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>'YTD CF'!F8-'YTD CF'!E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>'YTD CF'!G8-'YTD CF'!F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>'CASH FLOW'!D9-'YTD CF'!G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>'YTD CF'!H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>'YTD CF'!I8-'YTD CF'!H8</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>'YTD CF'!J8-'YTD CF'!I8</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>'CASH FLOW'!E9-'YTD CF'!J8</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>'YTD CF'!K8</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>'YTD CF'!L8-'YTD CF'!K8</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>'YTD CF'!M8-'YTD CF'!L8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="4">
+        <f>'CASH FLOW'!F9-'YTD CF'!M8</f>
+        <v/>
+      </c>
+      <c r="R8" s="4">
+        <f>'YTD CF'!N8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>'YTD CF'!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="4">
+        <f>'YTD CF'!C9-'YTD CF'!B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="4">
+        <f>'YTD CF'!D9-'YTD CF'!C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>'CASH FLOW'!C10-'YTD CF'!D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>'YTD CF'!E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>'YTD CF'!F9-'YTD CF'!E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>'YTD CF'!G9-'YTD CF'!F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>'CASH FLOW'!D10-'YTD CF'!G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>'YTD CF'!H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>'YTD CF'!I9-'YTD CF'!H9</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>'YTD CF'!J9-'YTD CF'!I9</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>'CASH FLOW'!E10-'YTD CF'!J9</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>'YTD CF'!K9</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>'YTD CF'!L9-'YTD CF'!K9</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>'YTD CF'!M9-'YTD CF'!L9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="4">
+        <f>'CASH FLOW'!F10-'YTD CF'!M9</f>
+        <v/>
+      </c>
+      <c r="R9" s="4">
+        <f>'YTD CF'!N9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Restructuring and Asset Impairment Charges</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>'YTD CF'!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>'YTD CF'!C10-'YTD CF'!B10</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>'YTD CF'!D10-'YTD CF'!C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>'CASH FLOW'!C11-'YTD CF'!D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>'YTD CF'!E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>'YTD CF'!F10-'YTD CF'!E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>'YTD CF'!G10-'YTD CF'!F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>'CASH FLOW'!D11-'YTD CF'!G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>'YTD CF'!H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>'YTD CF'!I10-'YTD CF'!H10</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>'YTD CF'!J10-'YTD CF'!I10</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>'CASH FLOW'!E11-'YTD CF'!J10</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>'YTD CF'!K10</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>'YTD CF'!L10-'YTD CF'!K10</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>'YTD CF'!M10-'YTD CF'!L10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4">
+        <f>'CASH FLOW'!F11-'YTD CF'!M10</f>
+        <v/>
+      </c>
+      <c r="R10" s="4">
+        <f>'YTD CF'!N10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Restructuring</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>'YTD CF'!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="4">
+        <f>'YTD CF'!C11-'YTD CF'!B11</f>
+        <v/>
+      </c>
+      <c r="D11" s="4">
+        <f>'YTD CF'!D11-'YTD CF'!C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="4">
+        <f>'CASH FLOW'!C12-'YTD CF'!D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>'YTD CF'!E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="4">
+        <f>'YTD CF'!F11-'YTD CF'!E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>'YTD CF'!G11-'YTD CF'!F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>'CASH FLOW'!D12-'YTD CF'!G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>'YTD CF'!H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>'YTD CF'!I11-'YTD CF'!H11</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>'YTD CF'!J11-'YTD CF'!I11</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>'CASH FLOW'!E12-'YTD CF'!J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>'YTD CF'!K11</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>'YTD CF'!L11-'YTD CF'!K11</f>
+        <v/>
+      </c>
+      <c r="P11" s="4">
+        <f>'YTD CF'!M11-'YTD CF'!L11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="4">
+        <f>'CASH FLOW'!F12-'YTD CF'!M11</f>
+        <v/>
+      </c>
+      <c r="R11" s="4">
+        <f>'YTD CF'!N11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Acquisition and Divestiture-Related Charges</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>'YTD CF'!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>'YTD CF'!C12-'YTD CF'!B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>'YTD CF'!D12-'YTD CF'!C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>'CASH FLOW'!C13-'YTD CF'!D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>'YTD CF'!E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>'YTD CF'!F12-'YTD CF'!E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>'YTD CF'!G12-'YTD CF'!F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>'CASH FLOW'!D13-'YTD CF'!G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>'YTD CF'!H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>'YTD CF'!I12-'YTD CF'!H12</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>'YTD CF'!J12-'YTD CF'!I12</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>'CASH FLOW'!E13-'YTD CF'!J12</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>'YTD CF'!K12</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>'YTD CF'!L12-'YTD CF'!K12</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>'YTD CF'!M12-'YTD CF'!L12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="4">
+        <f>'CASH FLOW'!F13-'YTD CF'!M12</f>
+        <v/>
+      </c>
+      <c r="R12" s="4">
+        <f>'YTD CF'!N12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cash Payments for Acquisition and Divestiture Costs</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <f>'YTD CF'!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="4">
+        <f>'YTD CF'!C13-'YTD CF'!B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="4">
+        <f>'YTD CF'!D13-'YTD CF'!C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="4">
+        <f>'CASH FLOW'!C14-'YTD CF'!D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>'YTD CF'!E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="4">
+        <f>'YTD CF'!F13-'YTD CF'!E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>'YTD CF'!G13-'YTD CF'!F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>'CASH FLOW'!D14-'YTD CF'!G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>'YTD CF'!H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>'YTD CF'!I13-'YTD CF'!H13</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>'YTD CF'!J13-'YTD CF'!I13</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>'CASH FLOW'!E14-'YTD CF'!J13</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>'YTD CF'!K13</f>
+        <v/>
+      </c>
+      <c r="O13" s="4">
+        <f>'YTD CF'!L13-'YTD CF'!K13</f>
+        <v/>
+      </c>
+      <c r="P13" s="4">
+        <f>'YTD CF'!M13-'YTD CF'!L13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="4">
+        <f>'CASH FLOW'!F14-'YTD CF'!M13</f>
+        <v/>
+      </c>
+      <c r="R13" s="4">
+        <f>'YTD CF'!N13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Pension and Postretirement Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <f>'YTD CF'!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="4">
+        <f>'YTD CF'!C14-'YTD CF'!B14</f>
+        <v/>
+      </c>
+      <c r="D14" s="4">
+        <f>'YTD CF'!D14-'YTD CF'!C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="4">
+        <f>'CASH FLOW'!C15-'YTD CF'!D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>'YTD CF'!E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>'YTD CF'!F14-'YTD CF'!E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>'YTD CF'!G14-'YTD CF'!F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>'CASH FLOW'!D15-'YTD CF'!G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>'YTD CF'!H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>'YTD CF'!I14-'YTD CF'!H14</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>'YTD CF'!J14-'YTD CF'!I14</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>'CASH FLOW'!E15-'YTD CF'!J14</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>'YTD CF'!K14</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>'YTD CF'!L14-'YTD CF'!K14</f>
+        <v/>
+      </c>
+      <c r="P14" s="4">
+        <f>'YTD CF'!M14-'YTD CF'!L14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="4">
+        <f>'CASH FLOW'!F15-'YTD CF'!M14</f>
+        <v/>
+      </c>
+      <c r="R14" s="4">
+        <f>'YTD CF'!N14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Pension and Postretirement Benefits Contributions</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>'YTD CF'!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="4">
+        <f>'YTD CF'!C15-'YTD CF'!B15</f>
+        <v/>
+      </c>
+      <c r="D15" s="4">
+        <f>'YTD CF'!D15-'YTD CF'!C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="4">
+        <f>'CASH FLOW'!C16-'YTD CF'!D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>'YTD CF'!E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>'YTD CF'!F15-'YTD CF'!E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>'YTD CF'!G15-'YTD CF'!F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>'CASH FLOW'!D16-'YTD CF'!G15</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>'YTD CF'!H15</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>'YTD CF'!I15-'YTD CF'!H15</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>'YTD CF'!J15-'YTD CF'!I15</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>'CASH FLOW'!E16-'YTD CF'!J15</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>'YTD CF'!K15</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>'YTD CF'!L15-'YTD CF'!K15</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>'YTD CF'!M15-'YTD CF'!L15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="4">
+        <f>'CASH FLOW'!F16-'YTD CF'!M15</f>
+        <v/>
+      </c>
+      <c r="R15" s="4">
+        <f>'YTD CF'!N15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>(Benefit) Provision for Deferred Income Taxes</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>'YTD CF'!B16</f>
+        <v/>
+      </c>
+      <c r="C16" s="4">
+        <f>'YTD CF'!C16-'YTD CF'!B16</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>'YTD CF'!D16-'YTD CF'!C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>'CASH FLOW'!C17-'YTD CF'!D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>'YTD CF'!E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>'YTD CF'!F16-'YTD CF'!E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>'YTD CF'!G16-'YTD CF'!F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>'CASH FLOW'!D17-'YTD CF'!G16</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>'YTD CF'!H16</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>'YTD CF'!I16-'YTD CF'!H16</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>'YTD CF'!J16-'YTD CF'!I16</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>'CASH FLOW'!E17-'YTD CF'!J16</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>'YTD CF'!K16</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>'YTD CF'!L16-'YTD CF'!K16</f>
+        <v/>
+      </c>
+      <c r="P16" s="4">
+        <f>'YTD CF'!M16-'YTD CF'!L16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="4">
+        <f>'CASH FLOW'!F17-'YTD CF'!M16</f>
+        <v/>
+      </c>
+      <c r="R16" s="4">
+        <f>'YTD CF'!N16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Tax Expense Related to TCJ Act</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>'YTD CF'!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="4">
+        <f>'YTD CF'!C17-'YTD CF'!B17</f>
+        <v/>
+      </c>
+      <c r="D17" s="4">
+        <f>'YTD CF'!D17-'YTD CF'!C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="4">
+        <f>'CASH FLOW'!C18-'YTD CF'!D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>'YTD CF'!E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>'YTD CF'!F17-'YTD CF'!E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>'YTD CF'!G17-'YTD CF'!F17</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>'CASH FLOW'!D18-'YTD CF'!G17</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>'YTD CF'!H17</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>'YTD CF'!I17-'YTD CF'!H17</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>'YTD CF'!J17-'YTD CF'!I17</f>
+        <v/>
+      </c>
+      <c r="M17" s="4">
+        <f>'CASH FLOW'!E18-'YTD CF'!J17</f>
+        <v/>
+      </c>
+      <c r="N17" s="4">
+        <f>'YTD CF'!K17</f>
+        <v/>
+      </c>
+      <c r="O17" s="4">
+        <f>'YTD CF'!L17-'YTD CF'!K17</f>
+        <v/>
+      </c>
+      <c r="P17" s="4">
+        <f>'YTD CF'!M17-'YTD CF'!L17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="4">
+        <f>'CASH FLOW'!F18-'YTD CF'!M17</f>
+        <v/>
+      </c>
+      <c r="R17" s="4">
+        <f>'YTD CF'!N17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tax Payments Related to TCJ Act</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <f>'YTD CF'!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="4">
+        <f>'YTD CF'!C18-'YTD CF'!B18</f>
+        <v/>
+      </c>
+      <c r="D18" s="4">
+        <f>'YTD CF'!D18-'YTD CF'!C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="4">
+        <f>'CASH FLOW'!C19-'YTD CF'!D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>'YTD CF'!E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>'YTD CF'!F18-'YTD CF'!E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>'YTD CF'!G18-'YTD CF'!F18</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>'CASH FLOW'!D19-'YTD CF'!G18</f>
+        <v/>
+      </c>
+      <c r="J18" s="4">
+        <f>'YTD CF'!H18</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>'YTD CF'!I18-'YTD CF'!H18</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>'YTD CF'!J18-'YTD CF'!I18</f>
+        <v/>
+      </c>
+      <c r="M18" s="4">
+        <f>'CASH FLOW'!E19-'YTD CF'!J18</f>
+        <v/>
+      </c>
+      <c r="N18" s="4">
+        <f>'YTD CF'!K18</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>'YTD CF'!L18-'YTD CF'!K18</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>'YTD CF'!M18-'YTD CF'!L18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="4">
+        <f>'CASH FLOW'!F19-'YTD CF'!M18</f>
+        <v/>
+      </c>
+      <c r="R18" s="4">
+        <f>'YTD CF'!N18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>'YTD CF'!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="4">
+        <f>'YTD CF'!C19-'YTD CF'!B19</f>
+        <v/>
+      </c>
+      <c r="D19" s="4">
+        <f>'YTD CF'!D19-'YTD CF'!C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="4">
+        <f>'CASH FLOW'!C20-'YTD CF'!D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>'YTD CF'!E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>'YTD CF'!F19-'YTD CF'!E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>'YTD CF'!G19-'YTD CF'!F19</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>'CASH FLOW'!D20-'YTD CF'!G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>'YTD CF'!H19</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>'YTD CF'!I19-'YTD CF'!H19</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>'YTD CF'!J19-'YTD CF'!I19</f>
+        <v/>
+      </c>
+      <c r="M19" s="4">
+        <f>'CASH FLOW'!E20-'YTD CF'!J19</f>
+        <v/>
+      </c>
+      <c r="N19" s="4">
+        <f>'YTD CF'!K19</f>
+        <v/>
+      </c>
+      <c r="O19" s="4">
+        <f>'YTD CF'!L19-'YTD CF'!K19</f>
+        <v/>
+      </c>
+      <c r="P19" s="4">
+        <f>'YTD CF'!M19-'YTD CF'!L19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="4">
+        <f>'CASH FLOW'!F20-'YTD CF'!M19</f>
+        <v/>
+      </c>
+      <c r="R19" s="4">
+        <f>'YTD CF'!N19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <f>'YTD CF'!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="4">
+        <f>'YTD CF'!C20-'YTD CF'!B20</f>
+        <v/>
+      </c>
+      <c r="D20" s="4">
+        <f>'YTD CF'!D20-'YTD CF'!C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>'CASH FLOW'!C21-'YTD CF'!D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>'YTD CF'!E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>'YTD CF'!F20-'YTD CF'!E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>'YTD CF'!G20-'YTD CF'!F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>'CASH FLOW'!D21-'YTD CF'!G20</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>'YTD CF'!H20</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>'YTD CF'!I20-'YTD CF'!H20</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>'YTD CF'!J20-'YTD CF'!I20</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>'CASH FLOW'!E21-'YTD CF'!J20</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>'YTD CF'!K20</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>'YTD CF'!L20-'YTD CF'!K20</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>'YTD CF'!M20-'YTD CF'!L20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="4">
+        <f>'CASH FLOW'!F21-'YTD CF'!M20</f>
+        <v/>
+      </c>
+      <c r="R20" s="4">
+        <f>'YTD CF'!N20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Prepaid Expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>'YTD CF'!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="4">
+        <f>'YTD CF'!C21-'YTD CF'!B21</f>
+        <v/>
+      </c>
+      <c r="D21" s="4">
+        <f>'YTD CF'!D21-'YTD CF'!C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="4">
+        <f>'CASH FLOW'!C22-'YTD CF'!D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>'YTD CF'!E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>'YTD CF'!F21-'YTD CF'!E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>'YTD CF'!G21-'YTD CF'!F21</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>'CASH FLOW'!D22-'YTD CF'!G21</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>'YTD CF'!H21</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>'YTD CF'!I21-'YTD CF'!H21</f>
+        <v/>
+      </c>
+      <c r="L21" s="4">
+        <f>'YTD CF'!J21-'YTD CF'!I21</f>
+        <v/>
+      </c>
+      <c r="M21" s="4">
+        <f>'CASH FLOW'!E22-'YTD CF'!J21</f>
+        <v/>
+      </c>
+      <c r="N21" s="4">
+        <f>'YTD CF'!K21</f>
+        <v/>
+      </c>
+      <c r="O21" s="4">
+        <f>'YTD CF'!L21-'YTD CF'!K21</f>
+        <v/>
+      </c>
+      <c r="P21" s="4">
+        <f>'YTD CF'!M21-'YTD CF'!L21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="4">
+        <f>'CASH FLOW'!F22-'YTD CF'!M21</f>
+        <v/>
+      </c>
+      <c r="R21" s="4">
+        <f>'YTD CF'!N21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B22" s="4">
+        <f>'YTD CF'!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="4">
+        <f>'YTD CF'!C22-'YTD CF'!B22</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>'YTD CF'!D22-'YTD CF'!C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>'CASH FLOW'!C23-'YTD CF'!D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>'YTD CF'!E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>'YTD CF'!F22-'YTD CF'!E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>'YTD CF'!G22-'YTD CF'!F22</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>'CASH FLOW'!D23-'YTD CF'!G22</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>'YTD CF'!H22</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>'YTD CF'!I22-'YTD CF'!H22</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>'YTD CF'!J22-'YTD CF'!I22</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>'CASH FLOW'!E23-'YTD CF'!J22</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>'YTD CF'!K22</f>
+        <v/>
+      </c>
+      <c r="O22" s="4">
+        <f>'YTD CF'!L22-'YTD CF'!K22</f>
+        <v/>
+      </c>
+      <c r="P22" s="4">
+        <f>'YTD CF'!M22-'YTD CF'!L22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="4">
+        <f>'CASH FLOW'!F23-'YTD CF'!M22</f>
+        <v/>
+      </c>
+      <c r="R22" s="4">
+        <f>'YTD CF'!N22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="4">
+        <f>'YTD CF'!B23</f>
+        <v/>
+      </c>
+      <c r="C23" s="4">
+        <f>'YTD CF'!C23-'YTD CF'!B23</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>'YTD CF'!D23-'YTD CF'!C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>'CASH FLOW'!C24-'YTD CF'!D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>'YTD CF'!E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>'YTD CF'!F23-'YTD CF'!E23</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>'YTD CF'!G23-'YTD CF'!F23</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>'CASH FLOW'!D24-'YTD CF'!G23</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>'YTD CF'!H23</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>'YTD CF'!I23-'YTD CF'!H23</f>
+        <v/>
+      </c>
+      <c r="L23" s="4">
+        <f>'YTD CF'!J23-'YTD CF'!I23</f>
+        <v/>
+      </c>
+      <c r="M23" s="4">
+        <f>'CASH FLOW'!E24-'YTD CF'!J23</f>
+        <v/>
+      </c>
+      <c r="N23" s="4">
+        <f>'YTD CF'!K23</f>
+        <v/>
+      </c>
+      <c r="O23" s="4">
+        <f>'YTD CF'!L23-'YTD CF'!K23</f>
+        <v/>
+      </c>
+      <c r="P23" s="4">
+        <f>'YTD CF'!M23-'YTD CF'!L23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="4">
+        <f>'CASH FLOW'!F24-'YTD CF'!M23</f>
+        <v/>
+      </c>
+      <c r="R23" s="4">
+        <f>'YTD CF'!N23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Other Operating Items</t>
+        </is>
+      </c>
+      <c r="B24" s="4">
+        <f>'YTD CF'!B24</f>
+        <v/>
+      </c>
+      <c r="C24" s="4">
+        <f>'YTD CF'!C24-'YTD CF'!B24</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f>'YTD CF'!D24-'YTD CF'!C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>'CASH FLOW'!C25-'YTD CF'!D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>'YTD CF'!E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>'YTD CF'!F24-'YTD CF'!E24</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>'YTD CF'!G24-'YTD CF'!F24</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>'CASH FLOW'!D25-'YTD CF'!G24</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>'YTD CF'!H24</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>'YTD CF'!I24-'YTD CF'!H24</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>'YTD CF'!J24-'YTD CF'!I24</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>'CASH FLOW'!E25-'YTD CF'!J24</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>'YTD CF'!K24</f>
+        <v/>
+      </c>
+      <c r="O24" s="4">
+        <f>'YTD CF'!L24-'YTD CF'!K24</f>
+        <v/>
+      </c>
+      <c r="P24" s="4">
+        <f>'YTD CF'!M24-'YTD CF'!L24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="4">
+        <f>'CASH FLOW'!F25-'YTD CF'!M24</f>
+        <v/>
+      </c>
+      <c r="R24" s="4">
+        <f>'YTD CF'!N24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Operations</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>'YTD CF'!B25</f>
+        <v/>
+      </c>
+      <c r="C25" s="6">
+        <f>'YTD CF'!C25-'YTD CF'!B25</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>'YTD CF'!D25-'YTD CF'!C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>'CASH FLOW'!C26-'YTD CF'!D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>'YTD CF'!E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>'YTD CF'!F25-'YTD CF'!E25</f>
+        <v/>
+      </c>
+      <c r="H25" s="6">
+        <f>'YTD CF'!G25-'YTD CF'!F25</f>
+        <v/>
+      </c>
+      <c r="I25" s="6">
+        <f>'CASH FLOW'!D26-'YTD CF'!G25</f>
+        <v/>
+      </c>
+      <c r="J25" s="6">
+        <f>'YTD CF'!H25</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>'YTD CF'!I25-'YTD CF'!H25</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>'YTD CF'!J25-'YTD CF'!I25</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>'CASH FLOW'!E26-'YTD CF'!J25</f>
+        <v/>
+      </c>
+      <c r="N25" s="6">
+        <f>'YTD CF'!K25</f>
+        <v/>
+      </c>
+      <c r="O25" s="6">
+        <f>'YTD CF'!L25-'YTD CF'!K25</f>
+        <v/>
+      </c>
+      <c r="P25" s="6">
+        <f>'YTD CF'!M25-'YTD CF'!L25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="6">
+        <f>'CASH FLOW'!F26-'YTD CF'!M25</f>
+        <v/>
+      </c>
+      <c r="R25" s="6">
+        <f>'YTD CF'!N25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Purchase of PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <f>'YTD CF'!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="4">
+        <f>'YTD CF'!C26-'YTD CF'!B26</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>'YTD CF'!D26-'YTD CF'!C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>'CASH FLOW'!C27-'YTD CF'!D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>'YTD CF'!E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>'YTD CF'!F26-'YTD CF'!E26</f>
+        <v/>
+      </c>
+      <c r="H26" s="4">
+        <f>'YTD CF'!G26-'YTD CF'!F26</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>'CASH FLOW'!D27-'YTD CF'!G26</f>
+        <v/>
+      </c>
+      <c r="J26" s="4">
+        <f>'YTD CF'!H26</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>'YTD CF'!I26-'YTD CF'!H26</f>
+        <v/>
+      </c>
+      <c r="L26" s="4">
+        <f>'YTD CF'!J26-'YTD CF'!I26</f>
+        <v/>
+      </c>
+      <c r="M26" s="4">
+        <f>'CASH FLOW'!E27-'YTD CF'!J26</f>
+        <v/>
+      </c>
+      <c r="N26" s="4">
+        <f>'YTD CF'!K26</f>
+        <v/>
+      </c>
+      <c r="O26" s="4">
+        <f>'YTD CF'!L26-'YTD CF'!K26</f>
+        <v/>
+      </c>
+      <c r="P26" s="4">
+        <f>'YTD CF'!M26-'YTD CF'!L26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="4">
+        <f>'CASH FLOW'!F27-'YTD CF'!M26</f>
+        <v/>
+      </c>
+      <c r="R26" s="4">
+        <f>'YTD CF'!N26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Sale of Assets</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>'YTD CF'!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="4">
+        <f>'YTD CF'!C27-'YTD CF'!B27</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>'YTD CF'!D27-'YTD CF'!C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f>'CASH FLOW'!C28-'YTD CF'!D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>'YTD CF'!E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="4">
+        <f>'YTD CF'!F27-'YTD CF'!E27</f>
+        <v/>
+      </c>
+      <c r="H27" s="4">
+        <f>'YTD CF'!G27-'YTD CF'!F27</f>
+        <v/>
+      </c>
+      <c r="I27" s="4">
+        <f>'CASH FLOW'!D28-'YTD CF'!G27</f>
+        <v/>
+      </c>
+      <c r="J27" s="4">
+        <f>'YTD CF'!H27</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>'YTD CF'!I27-'YTD CF'!H27</f>
+        <v/>
+      </c>
+      <c r="L27" s="4">
+        <f>'YTD CF'!J27-'YTD CF'!I27</f>
+        <v/>
+      </c>
+      <c r="M27" s="4">
+        <f>'CASH FLOW'!E28-'YTD CF'!J27</f>
+        <v/>
+      </c>
+      <c r="N27" s="4">
+        <f>'YTD CF'!K27</f>
+        <v/>
+      </c>
+      <c r="O27" s="4">
+        <f>'YTD CF'!L27-'YTD CF'!K27</f>
+        <v/>
+      </c>
+      <c r="P27" s="4">
+        <f>'YTD CF'!M27-'YTD CF'!L27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="4">
+        <f>'CASH FLOW'!F28-'YTD CF'!M27</f>
+        <v/>
+      </c>
+      <c r="R27" s="4">
+        <f>'YTD CF'!N27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Acquisitions, Net of Cash Acquired</t>
+        </is>
+      </c>
+      <c r="B28" s="4">
+        <f>'YTD CF'!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="4">
+        <f>'YTD CF'!C28-'YTD CF'!B28</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f>'YTD CF'!D28-'YTD CF'!C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f>'CASH FLOW'!C29-'YTD CF'!D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f>'YTD CF'!E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="4">
+        <f>'YTD CF'!F28-'YTD CF'!E28</f>
+        <v/>
+      </c>
+      <c r="H28" s="4">
+        <f>'YTD CF'!G28-'YTD CF'!F28</f>
+        <v/>
+      </c>
+      <c r="I28" s="4">
+        <f>'CASH FLOW'!D29-'YTD CF'!G28</f>
+        <v/>
+      </c>
+      <c r="J28" s="4">
+        <f>'YTD CF'!H28</f>
+        <v/>
+      </c>
+      <c r="K28" s="4">
+        <f>'YTD CF'!I28-'YTD CF'!H28</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>'YTD CF'!J28-'YTD CF'!I28</f>
+        <v/>
+      </c>
+      <c r="M28" s="4">
+        <f>'CASH FLOW'!E29-'YTD CF'!J28</f>
+        <v/>
+      </c>
+      <c r="N28" s="4">
+        <f>'YTD CF'!K28</f>
+        <v/>
+      </c>
+      <c r="O28" s="4">
+        <f>'YTD CF'!L28-'YTD CF'!K28</f>
+        <v/>
+      </c>
+      <c r="P28" s="4">
+        <f>'YTD CF'!M28-'YTD CF'!L28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="4">
+        <f>'CASH FLOW'!F29-'YTD CF'!M28</f>
+        <v/>
+      </c>
+      <c r="R28" s="4">
+        <f>'YTD CF'!N28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Juice Transaction</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>'YTD CF'!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="4">
+        <f>'YTD CF'!C29-'YTD CF'!B29</f>
+        <v/>
+      </c>
+      <c r="D29" s="4">
+        <f>'YTD CF'!D29-'YTD CF'!C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="4">
+        <f>'CASH FLOW'!C30-'YTD CF'!D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f>'YTD CF'!E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="4">
+        <f>'YTD CF'!F29-'YTD CF'!E29</f>
+        <v/>
+      </c>
+      <c r="H29" s="4">
+        <f>'YTD CF'!G29-'YTD CF'!F29</f>
+        <v/>
+      </c>
+      <c r="I29" s="4">
+        <f>'CASH FLOW'!D30-'YTD CF'!G29</f>
+        <v/>
+      </c>
+      <c r="J29" s="4">
+        <f>'YTD CF'!H29</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>'YTD CF'!I29-'YTD CF'!H29</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>'YTD CF'!J29-'YTD CF'!I29</f>
+        <v/>
+      </c>
+      <c r="M29" s="4">
+        <f>'CASH FLOW'!E30-'YTD CF'!J29</f>
+        <v/>
+      </c>
+      <c r="N29" s="4">
+        <f>'YTD CF'!K29</f>
+        <v/>
+      </c>
+      <c r="O29" s="4">
+        <f>'YTD CF'!L29-'YTD CF'!K29</f>
+        <v/>
+      </c>
+      <c r="P29" s="4">
+        <f>'YTD CF'!M29-'YTD CF'!L29</f>
+        <v/>
+      </c>
+      <c r="Q29" s="4">
+        <f>'CASH FLOW'!F30-'YTD CF'!M29</f>
+        <v/>
+      </c>
+      <c r="R29" s="4">
+        <f>'YTD CF'!N29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Divestitures of Businesses</t>
+        </is>
+      </c>
+      <c r="B30" s="4">
+        <f>'YTD CF'!B30</f>
+        <v/>
+      </c>
+      <c r="C30" s="4">
+        <f>'YTD CF'!C30-'YTD CF'!B30</f>
+        <v/>
+      </c>
+      <c r="D30" s="4">
+        <f>'YTD CF'!D30-'YTD CF'!C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="4">
+        <f>'CASH FLOW'!C31-'YTD CF'!D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f>'YTD CF'!E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="4">
+        <f>'YTD CF'!F30-'YTD CF'!E30</f>
+        <v/>
+      </c>
+      <c r="H30" s="4">
+        <f>'YTD CF'!G30-'YTD CF'!F30</f>
+        <v/>
+      </c>
+      <c r="I30" s="4">
+        <f>'CASH FLOW'!D31-'YTD CF'!G30</f>
+        <v/>
+      </c>
+      <c r="J30" s="4">
+        <f>'YTD CF'!H30</f>
+        <v/>
+      </c>
+      <c r="K30" s="4">
+        <f>'YTD CF'!I30-'YTD CF'!H30</f>
+        <v/>
+      </c>
+      <c r="L30" s="4">
+        <f>'YTD CF'!J30-'YTD CF'!I30</f>
+        <v/>
+      </c>
+      <c r="M30" s="4">
+        <f>'CASH FLOW'!E31-'YTD CF'!J30</f>
+        <v/>
+      </c>
+      <c r="N30" s="4">
+        <f>'YTD CF'!K30</f>
+        <v/>
+      </c>
+      <c r="O30" s="4">
+        <f>'YTD CF'!L30-'YTD CF'!K30</f>
+        <v/>
+      </c>
+      <c r="P30" s="4">
+        <f>'YTD CF'!M30-'YTD CF'!L30</f>
+        <v/>
+      </c>
+      <c r="Q30" s="4">
+        <f>'CASH FLOW'!F31-'YTD CF'!M30</f>
+        <v/>
+      </c>
+      <c r="R30" s="4">
+        <f>'YTD CF'!N30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Short-Term Investments</t>
+        </is>
+      </c>
+      <c r="B31" s="4">
+        <f>'YTD CF'!B31</f>
+        <v/>
+      </c>
+      <c r="C31" s="4">
+        <f>'YTD CF'!C31-'YTD CF'!B31</f>
+        <v/>
+      </c>
+      <c r="D31" s="4">
+        <f>'YTD CF'!D31-'YTD CF'!C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="4">
+        <f>'CASH FLOW'!C32-'YTD CF'!D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f>'YTD CF'!E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>'YTD CF'!F31-'YTD CF'!E31</f>
+        <v/>
+      </c>
+      <c r="H31" s="4">
+        <f>'YTD CF'!G31-'YTD CF'!F31</f>
+        <v/>
+      </c>
+      <c r="I31" s="4">
+        <f>'CASH FLOW'!D32-'YTD CF'!G31</f>
+        <v/>
+      </c>
+      <c r="J31" s="4">
+        <f>'YTD CF'!H31</f>
+        <v/>
+      </c>
+      <c r="K31" s="4">
+        <f>'YTD CF'!I31-'YTD CF'!H31</f>
+        <v/>
+      </c>
+      <c r="L31" s="4">
+        <f>'YTD CF'!J31-'YTD CF'!I31</f>
+        <v/>
+      </c>
+      <c r="M31" s="4">
+        <f>'CASH FLOW'!E32-'YTD CF'!J31</f>
+        <v/>
+      </c>
+      <c r="N31" s="4">
+        <f>'YTD CF'!K31</f>
+        <v/>
+      </c>
+      <c r="O31" s="4">
+        <f>'YTD CF'!L31-'YTD CF'!K31</f>
+        <v/>
+      </c>
+      <c r="P31" s="4">
+        <f>'YTD CF'!M31-'YTD CF'!L31</f>
+        <v/>
+      </c>
+      <c r="Q31" s="4">
+        <f>'CASH FLOW'!F32-'YTD CF'!M31</f>
+        <v/>
+      </c>
+      <c r="R31" s="4">
+        <f>'YTD CF'!N31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Other Investing Activities</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>'YTD CF'!B32</f>
+        <v/>
+      </c>
+      <c r="C32" s="4">
+        <f>'YTD CF'!C32-'YTD CF'!B32</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>'YTD CF'!D32-'YTD CF'!C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f>'CASH FLOW'!C33-'YTD CF'!D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>'YTD CF'!E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>'YTD CF'!F32-'YTD CF'!E32</f>
+        <v/>
+      </c>
+      <c r="H32" s="4">
+        <f>'YTD CF'!G32-'YTD CF'!F32</f>
+        <v/>
+      </c>
+      <c r="I32" s="4">
+        <f>'CASH FLOW'!D33-'YTD CF'!G32</f>
+        <v/>
+      </c>
+      <c r="J32" s="4">
+        <f>'YTD CF'!H32</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>'YTD CF'!I32-'YTD CF'!H32</f>
+        <v/>
+      </c>
+      <c r="L32" s="4">
+        <f>'YTD CF'!J32-'YTD CF'!I32</f>
+        <v/>
+      </c>
+      <c r="M32" s="4">
+        <f>'CASH FLOW'!E33-'YTD CF'!J32</f>
+        <v/>
+      </c>
+      <c r="N32" s="4">
+        <f>'YTD CF'!K32</f>
+        <v/>
+      </c>
+      <c r="O32" s="4">
+        <f>'YTD CF'!L32-'YTD CF'!K32</f>
+        <v/>
+      </c>
+      <c r="P32" s="4">
+        <f>'YTD CF'!M32-'YTD CF'!L32</f>
+        <v/>
+      </c>
+      <c r="Q32" s="4">
+        <f>'CASH FLOW'!F33-'YTD CF'!M32</f>
+        <v/>
+      </c>
+      <c r="R32" s="4">
+        <f>'YTD CF'!N32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Investing</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>'YTD CF'!B33</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>'YTD CF'!C33-'YTD CF'!B33</f>
+        <v/>
+      </c>
+      <c r="D33" s="6">
+        <f>'YTD CF'!D33-'YTD CF'!C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>'CASH FLOW'!C34-'YTD CF'!D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="6">
+        <f>'YTD CF'!E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="6">
+        <f>'YTD CF'!F33-'YTD CF'!E33</f>
+        <v/>
+      </c>
+      <c r="H33" s="6">
+        <f>'YTD CF'!G33-'YTD CF'!F33</f>
+        <v/>
+      </c>
+      <c r="I33" s="6">
+        <f>'CASH FLOW'!D34-'YTD CF'!G33</f>
+        <v/>
+      </c>
+      <c r="J33" s="6">
+        <f>'YTD CF'!H33</f>
+        <v/>
+      </c>
+      <c r="K33" s="6">
+        <f>'YTD CF'!I33-'YTD CF'!H33</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f>'YTD CF'!J33-'YTD CF'!I33</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>'CASH FLOW'!E34-'YTD CF'!J33</f>
+        <v/>
+      </c>
+      <c r="N33" s="6">
+        <f>'YTD CF'!K33</f>
+        <v/>
+      </c>
+      <c r="O33" s="6">
+        <f>'YTD CF'!L33-'YTD CF'!K33</f>
+        <v/>
+      </c>
+      <c r="P33" s="6">
+        <f>'YTD CF'!M33-'YTD CF'!L33</f>
+        <v/>
+      </c>
+      <c r="Q33" s="6">
+        <f>'CASH FLOW'!F34-'YTD CF'!M33</f>
+        <v/>
+      </c>
+      <c r="R33" s="6">
+        <f>'YTD CF'!N33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Issuance of Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>'YTD CF'!B34</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>'YTD CF'!C34-'YTD CF'!B34</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>'YTD CF'!D34-'YTD CF'!C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>'CASH FLOW'!C35-'YTD CF'!D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>'YTD CF'!E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>'YTD CF'!F34-'YTD CF'!E34</f>
+        <v/>
+      </c>
+      <c r="H34" s="4">
+        <f>'YTD CF'!G34-'YTD CF'!F34</f>
+        <v/>
+      </c>
+      <c r="I34" s="4">
+        <f>'CASH FLOW'!D35-'YTD CF'!G34</f>
+        <v/>
+      </c>
+      <c r="J34" s="4">
+        <f>'YTD CF'!H34</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>'YTD CF'!I34-'YTD CF'!H34</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>'YTD CF'!J34-'YTD CF'!I34</f>
+        <v/>
+      </c>
+      <c r="M34" s="4">
+        <f>'CASH FLOW'!E35-'YTD CF'!J34</f>
+        <v/>
+      </c>
+      <c r="N34" s="4">
+        <f>'YTD CF'!K34</f>
+        <v/>
+      </c>
+      <c r="O34" s="4">
+        <f>'YTD CF'!L34-'YTD CF'!K34</f>
+        <v/>
+      </c>
+      <c r="P34" s="4">
+        <f>'YTD CF'!M34-'YTD CF'!L34</f>
+        <v/>
+      </c>
+      <c r="Q34" s="4">
+        <f>'CASH FLOW'!F35-'YTD CF'!M34</f>
+        <v/>
+      </c>
+      <c r="R34" s="4">
+        <f>'YTD CF'!N34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Repayments of Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>'YTD CF'!B35</f>
+        <v/>
+      </c>
+      <c r="C35" s="4">
+        <f>'YTD CF'!C35-'YTD CF'!B35</f>
+        <v/>
+      </c>
+      <c r="D35" s="4">
+        <f>'YTD CF'!D35-'YTD CF'!C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>'CASH FLOW'!C36-'YTD CF'!D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>'YTD CF'!E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>'YTD CF'!F35-'YTD CF'!E35</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>'YTD CF'!G35-'YTD CF'!F35</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>'CASH FLOW'!D36-'YTD CF'!G35</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>'YTD CF'!H35</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>'YTD CF'!I35-'YTD CF'!H35</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>'YTD CF'!J35-'YTD CF'!I35</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>'CASH FLOW'!E36-'YTD CF'!J35</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>'YTD CF'!K35</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>'YTD CF'!L35-'YTD CF'!K35</f>
+        <v/>
+      </c>
+      <c r="P35" s="4">
+        <f>'YTD CF'!M35-'YTD CF'!L35</f>
+        <v/>
+      </c>
+      <c r="Q35" s="4">
+        <f>'CASH FLOW'!F36-'YTD CF'!M35</f>
+        <v/>
+      </c>
+      <c r="R35" s="4">
+        <f>'YTD CF'!N35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>'YTD CF'!B36</f>
+        <v/>
+      </c>
+      <c r="C36" s="4">
+        <f>'YTD CF'!C36-'YTD CF'!B36</f>
+        <v/>
+      </c>
+      <c r="D36" s="4">
+        <f>'YTD CF'!D36-'YTD CF'!C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>'CASH FLOW'!C37-'YTD CF'!D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>'YTD CF'!E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>'YTD CF'!F36-'YTD CF'!E36</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>'YTD CF'!G36-'YTD CF'!F36</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>'CASH FLOW'!D37-'YTD CF'!G36</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>'YTD CF'!H36</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>'YTD CF'!I36-'YTD CF'!H36</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>'YTD CF'!J36-'YTD CF'!I36</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>'CASH FLOW'!E37-'YTD CF'!J36</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>'YTD CF'!K36</f>
+        <v/>
+      </c>
+      <c r="O36" s="4">
+        <f>'YTD CF'!L36-'YTD CF'!K36</f>
+        <v/>
+      </c>
+      <c r="P36" s="4">
+        <f>'YTD CF'!M36-'YTD CF'!L36</f>
+        <v/>
+      </c>
+      <c r="Q36" s="4">
+        <f>'CASH FLOW'!F37-'YTD CF'!M36</f>
+        <v/>
+      </c>
+      <c r="R36" s="4">
+        <f>'YTD CF'!N36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Repayments of Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>'YTD CF'!B37</f>
+        <v/>
+      </c>
+      <c r="C37" s="4">
+        <f>'YTD CF'!C37-'YTD CF'!B37</f>
+        <v/>
+      </c>
+      <c r="D37" s="4">
+        <f>'YTD CF'!D37-'YTD CF'!C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>'CASH FLOW'!C38-'YTD CF'!D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>'YTD CF'!E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>'YTD CF'!F37-'YTD CF'!E37</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>'YTD CF'!G37-'YTD CF'!F37</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>'CASH FLOW'!D38-'YTD CF'!G37</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>'YTD CF'!H37</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>'YTD CF'!I37-'YTD CF'!H37</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>'YTD CF'!J37-'YTD CF'!I37</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>'CASH FLOW'!E38-'YTD CF'!J37</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>'YTD CF'!K37</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>'YTD CF'!L37-'YTD CF'!K37</f>
+        <v/>
+      </c>
+      <c r="P37" s="4">
+        <f>'YTD CF'!M37-'YTD CF'!L37</f>
+        <v/>
+      </c>
+      <c r="Q37" s="4">
+        <f>'CASH FLOW'!F38-'YTD CF'!M37</f>
+        <v/>
+      </c>
+      <c r="R37" s="4">
+        <f>'YTD CF'!N37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Other Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="4">
+        <f>'YTD CF'!B38</f>
+        <v/>
+      </c>
+      <c r="C38" s="4">
+        <f>'YTD CF'!C38-'YTD CF'!B38</f>
+        <v/>
+      </c>
+      <c r="D38" s="4">
+        <f>'YTD CF'!D38-'YTD CF'!C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>'CASH FLOW'!C39-'YTD CF'!D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>'YTD CF'!E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>'YTD CF'!F38-'YTD CF'!E38</f>
+        <v/>
+      </c>
+      <c r="H38" s="4">
+        <f>'YTD CF'!G38-'YTD CF'!F38</f>
+        <v/>
+      </c>
+      <c r="I38" s="4">
+        <f>'CASH FLOW'!D39-'YTD CF'!G38</f>
+        <v/>
+      </c>
+      <c r="J38" s="4">
+        <f>'YTD CF'!H38</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>'YTD CF'!I38-'YTD CF'!H38</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>'YTD CF'!J38-'YTD CF'!I38</f>
+        <v/>
+      </c>
+      <c r="M38" s="4">
+        <f>'CASH FLOW'!E39-'YTD CF'!J38</f>
+        <v/>
+      </c>
+      <c r="N38" s="4">
+        <f>'YTD CF'!K38</f>
+        <v/>
+      </c>
+      <c r="O38" s="4">
+        <f>'YTD CF'!L38-'YTD CF'!K38</f>
+        <v/>
+      </c>
+      <c r="P38" s="4">
+        <f>'YTD CF'!M38-'YTD CF'!L38</f>
+        <v/>
+      </c>
+      <c r="Q38" s="4">
+        <f>'CASH FLOW'!F39-'YTD CF'!M38</f>
+        <v/>
+      </c>
+      <c r="R38" s="4">
+        <f>'YTD CF'!N38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Common Dividends</t>
+        </is>
+      </c>
+      <c r="B39" s="4">
+        <f>'YTD CF'!B39</f>
+        <v/>
+      </c>
+      <c r="C39" s="4">
+        <f>'YTD CF'!C39-'YTD CF'!B39</f>
+        <v/>
+      </c>
+      <c r="D39" s="4">
+        <f>'YTD CF'!D39-'YTD CF'!C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>'CASH FLOW'!C41-'YTD CF'!D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>'YTD CF'!E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>'YTD CF'!F39-'YTD CF'!E39</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>'YTD CF'!G39-'YTD CF'!F39</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>'CASH FLOW'!D41-'YTD CF'!G39</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>'YTD CF'!H39</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>'YTD CF'!I39-'YTD CF'!H39</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>'YTD CF'!J39-'YTD CF'!I39</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>'CASH FLOW'!E41-'YTD CF'!J39</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>'YTD CF'!K39</f>
+        <v/>
+      </c>
+      <c r="O39" s="4">
+        <f>'YTD CF'!L39-'YTD CF'!K39</f>
+        <v/>
+      </c>
+      <c r="P39" s="4">
+        <f>'YTD CF'!M39-'YTD CF'!L39</f>
+        <v/>
+      </c>
+      <c r="Q39" s="4">
+        <f>'CASH FLOW'!F41-'YTD CF'!M39</f>
+        <v/>
+      </c>
+      <c r="R39" s="4">
+        <f>'YTD CF'!N39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Share Repurchases</t>
+        </is>
+      </c>
+      <c r="B40" s="4">
+        <f>'YTD CF'!B40</f>
+        <v/>
+      </c>
+      <c r="C40" s="4">
+        <f>'YTD CF'!C40-'YTD CF'!B40</f>
+        <v/>
+      </c>
+      <c r="D40" s="4">
+        <f>'YTD CF'!D40-'YTD CF'!C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="4">
+        <f>'CASH FLOW'!C42-'YTD CF'!D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="4">
+        <f>'YTD CF'!E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="4">
+        <f>'YTD CF'!F40-'YTD CF'!E40</f>
+        <v/>
+      </c>
+      <c r="H40" s="4">
+        <f>'YTD CF'!G40-'YTD CF'!F40</f>
+        <v/>
+      </c>
+      <c r="I40" s="4">
+        <f>'CASH FLOW'!D42-'YTD CF'!G40</f>
+        <v/>
+      </c>
+      <c r="J40" s="4">
+        <f>'YTD CF'!H40</f>
+        <v/>
+      </c>
+      <c r="K40" s="4">
+        <f>'YTD CF'!I40-'YTD CF'!H40</f>
+        <v/>
+      </c>
+      <c r="L40" s="4">
+        <f>'YTD CF'!J40-'YTD CF'!I40</f>
+        <v/>
+      </c>
+      <c r="M40" s="4">
+        <f>'CASH FLOW'!E42-'YTD CF'!J40</f>
+        <v/>
+      </c>
+      <c r="N40" s="4">
+        <f>'YTD CF'!K40</f>
+        <v/>
+      </c>
+      <c r="O40" s="4">
+        <f>'YTD CF'!L40-'YTD CF'!K40</f>
+        <v/>
+      </c>
+      <c r="P40" s="4">
+        <f>'YTD CF'!M40-'YTD CF'!L40</f>
+        <v/>
+      </c>
+      <c r="Q40" s="4">
+        <f>'CASH FLOW'!F42-'YTD CF'!M40</f>
+        <v/>
+      </c>
+      <c r="R40" s="4">
+        <f>'YTD CF'!N40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Proceeds from Exercise of Stock Options</t>
+        </is>
+      </c>
+      <c r="B41" s="4">
+        <f>'YTD CF'!B41</f>
+        <v/>
+      </c>
+      <c r="C41" s="4">
+        <f>'YTD CF'!C41-'YTD CF'!B41</f>
+        <v/>
+      </c>
+      <c r="D41" s="4">
+        <f>'YTD CF'!D41-'YTD CF'!C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="4">
+        <f>'CASH FLOW'!C43-'YTD CF'!D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="4">
+        <f>'YTD CF'!E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="4">
+        <f>'YTD CF'!F41-'YTD CF'!E41</f>
+        <v/>
+      </c>
+      <c r="H41" s="4">
+        <f>'YTD CF'!G41-'YTD CF'!F41</f>
+        <v/>
+      </c>
+      <c r="I41" s="4">
+        <f>'CASH FLOW'!D43-'YTD CF'!G41</f>
+        <v/>
+      </c>
+      <c r="J41" s="4">
+        <f>'YTD CF'!H41</f>
+        <v/>
+      </c>
+      <c r="K41" s="4">
+        <f>'YTD CF'!I41-'YTD CF'!H41</f>
+        <v/>
+      </c>
+      <c r="L41" s="4">
+        <f>'YTD CF'!J41-'YTD CF'!I41</f>
+        <v/>
+      </c>
+      <c r="M41" s="4">
+        <f>'CASH FLOW'!E43-'YTD CF'!J41</f>
+        <v/>
+      </c>
+      <c r="N41" s="4">
+        <f>'YTD CF'!K41</f>
+        <v/>
+      </c>
+      <c r="O41" s="4">
+        <f>'YTD CF'!L41-'YTD CF'!K41</f>
+        <v/>
+      </c>
+      <c r="P41" s="4">
+        <f>'YTD CF'!M41-'YTD CF'!L41</f>
+        <v/>
+      </c>
+      <c r="Q41" s="4">
+        <f>'CASH FLOW'!F43-'YTD CF'!M41</f>
+        <v/>
+      </c>
+      <c r="R41" s="4">
+        <f>'YTD CF'!N41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Tax Withholdings on RSU/PSU Settlement</t>
+        </is>
+      </c>
+      <c r="B42" s="4">
+        <f>'YTD CF'!B42</f>
+        <v/>
+      </c>
+      <c r="C42" s="4">
+        <f>'YTD CF'!C42-'YTD CF'!B42</f>
+        <v/>
+      </c>
+      <c r="D42" s="4">
+        <f>'YTD CF'!D42-'YTD CF'!C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="4">
+        <f>'CASH FLOW'!C44-'YTD CF'!D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="4">
+        <f>'YTD CF'!E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="4">
+        <f>'YTD CF'!F42-'YTD CF'!E42</f>
+        <v/>
+      </c>
+      <c r="H42" s="4">
+        <f>'YTD CF'!G42-'YTD CF'!F42</f>
+        <v/>
+      </c>
+      <c r="I42" s="4">
+        <f>'CASH FLOW'!D44-'YTD CF'!G42</f>
+        <v/>
+      </c>
+      <c r="J42" s="4">
+        <f>'YTD CF'!H42</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>'YTD CF'!I42-'YTD CF'!H42</f>
+        <v/>
+      </c>
+      <c r="L42" s="4">
+        <f>'YTD CF'!J42-'YTD CF'!I42</f>
+        <v/>
+      </c>
+      <c r="M42" s="4">
+        <f>'CASH FLOW'!E44-'YTD CF'!J42</f>
+        <v/>
+      </c>
+      <c r="N42" s="4">
+        <f>'YTD CF'!K42</f>
+        <v/>
+      </c>
+      <c r="O42" s="4">
+        <f>'YTD CF'!L42-'YTD CF'!K42</f>
+        <v/>
+      </c>
+      <c r="P42" s="4">
+        <f>'YTD CF'!M42-'YTD CF'!L42</f>
+        <v/>
+      </c>
+      <c r="Q42" s="4">
+        <f>'CASH FLOW'!F44-'YTD CF'!M42</f>
+        <v/>
+      </c>
+      <c r="R42" s="4">
+        <f>'YTD CF'!N42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Other Financing Activities</t>
+        </is>
+      </c>
+      <c r="B43" s="4">
+        <f>'YTD CF'!B43</f>
+        <v/>
+      </c>
+      <c r="C43" s="4">
+        <f>'YTD CF'!C43-'YTD CF'!B43</f>
+        <v/>
+      </c>
+      <c r="D43" s="4">
+        <f>'YTD CF'!D43-'YTD CF'!C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="4">
+        <f>'CASH FLOW'!C45-'YTD CF'!D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="4">
+        <f>'YTD CF'!E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="4">
+        <f>'YTD CF'!F43-'YTD CF'!E43</f>
+        <v/>
+      </c>
+      <c r="H43" s="4">
+        <f>'YTD CF'!G43-'YTD CF'!F43</f>
+        <v/>
+      </c>
+      <c r="I43" s="4">
+        <f>'CASH FLOW'!D45-'YTD CF'!G43</f>
+        <v/>
+      </c>
+      <c r="J43" s="4">
+        <f>'YTD CF'!H43</f>
+        <v/>
+      </c>
+      <c r="K43" s="4">
+        <f>'YTD CF'!I43-'YTD CF'!H43</f>
+        <v/>
+      </c>
+      <c r="L43" s="4">
+        <f>'YTD CF'!J43-'YTD CF'!I43</f>
+        <v/>
+      </c>
+      <c r="M43" s="4">
+        <f>'CASH FLOW'!E45-'YTD CF'!J43</f>
+        <v/>
+      </c>
+      <c r="N43" s="4">
+        <f>'YTD CF'!K43</f>
+        <v/>
+      </c>
+      <c r="O43" s="4">
+        <f>'YTD CF'!L43-'YTD CF'!K43</f>
+        <v/>
+      </c>
+      <c r="P43" s="4">
+        <f>'YTD CF'!M43-'YTD CF'!L43</f>
+        <v/>
+      </c>
+      <c r="Q43" s="4">
+        <f>'CASH FLOW'!F45-'YTD CF'!M43</f>
+        <v/>
+      </c>
+      <c r="R43" s="4">
+        <f>'YTD CF'!N43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow from Financing</t>
+        </is>
+      </c>
+      <c r="B44" s="6">
+        <f>'YTD CF'!B44</f>
+        <v/>
+      </c>
+      <c r="C44" s="6">
+        <f>'YTD CF'!C44-'YTD CF'!B44</f>
+        <v/>
+      </c>
+      <c r="D44" s="6">
+        <f>'YTD CF'!D44-'YTD CF'!C44</f>
+        <v/>
+      </c>
+      <c r="E44" s="6">
+        <f>'CASH FLOW'!C46-'YTD CF'!D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="6">
+        <f>'YTD CF'!E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="6">
+        <f>'YTD CF'!F44-'YTD CF'!E44</f>
+        <v/>
+      </c>
+      <c r="H44" s="6">
+        <f>'YTD CF'!G44-'YTD CF'!F44</f>
+        <v/>
+      </c>
+      <c r="I44" s="6">
+        <f>'CASH FLOW'!D46-'YTD CF'!G44</f>
+        <v/>
+      </c>
+      <c r="J44" s="6">
+        <f>'YTD CF'!H44</f>
+        <v/>
+      </c>
+      <c r="K44" s="6">
+        <f>'YTD CF'!I44-'YTD CF'!H44</f>
+        <v/>
+      </c>
+      <c r="L44" s="6">
+        <f>'YTD CF'!J44-'YTD CF'!I44</f>
+        <v/>
+      </c>
+      <c r="M44" s="6">
+        <f>'CASH FLOW'!E46-'YTD CF'!J44</f>
+        <v/>
+      </c>
+      <c r="N44" s="6">
+        <f>'YTD CF'!K44</f>
+        <v/>
+      </c>
+      <c r="O44" s="6">
+        <f>'YTD CF'!L44-'YTD CF'!K44</f>
+        <v/>
+      </c>
+      <c r="P44" s="6">
+        <f>'YTD CF'!M44-'YTD CF'!L44</f>
+        <v/>
+      </c>
+      <c r="Q44" s="6">
+        <f>'CASH FLOW'!F46-'YTD CF'!M44</f>
+        <v/>
+      </c>
+      <c r="R44" s="6">
+        <f>'YTD CF'!N44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FX Effect on Cash</t>
+        </is>
+      </c>
+      <c r="B45" s="4">
+        <f>'YTD CF'!B45</f>
+        <v/>
+      </c>
+      <c r="C45" s="4">
+        <f>'YTD CF'!C45-'YTD CF'!B45</f>
+        <v/>
+      </c>
+      <c r="D45" s="4">
+        <f>'YTD CF'!D45-'YTD CF'!C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="4">
+        <f>'CASH FLOW'!C47-'YTD CF'!D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="4">
+        <f>'YTD CF'!E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="4">
+        <f>'YTD CF'!F45-'YTD CF'!E45</f>
+        <v/>
+      </c>
+      <c r="H45" s="4">
+        <f>'YTD CF'!G45-'YTD CF'!F45</f>
+        <v/>
+      </c>
+      <c r="I45" s="4">
+        <f>'CASH FLOW'!D47-'YTD CF'!G45</f>
+        <v/>
+      </c>
+      <c r="J45" s="4">
+        <f>'YTD CF'!H45</f>
+        <v/>
+      </c>
+      <c r="K45" s="4">
+        <f>'YTD CF'!I45-'YTD CF'!H45</f>
+        <v/>
+      </c>
+      <c r="L45" s="4">
+        <f>'YTD CF'!J45-'YTD CF'!I45</f>
+        <v/>
+      </c>
+      <c r="M45" s="4">
+        <f>'CASH FLOW'!E47-'YTD CF'!J45</f>
+        <v/>
+      </c>
+      <c r="N45" s="4">
+        <f>'YTD CF'!K45</f>
+        <v/>
+      </c>
+      <c r="O45" s="4">
+        <f>'YTD CF'!L45-'YTD CF'!K45</f>
+        <v/>
+      </c>
+      <c r="P45" s="4">
+        <f>'YTD CF'!M45-'YTD CF'!L45</f>
+        <v/>
+      </c>
+      <c r="Q45" s="4">
+        <f>'CASH FLOW'!F47-'YTD CF'!M45</f>
+        <v/>
+      </c>
+      <c r="R45" s="4">
+        <f>'YTD CF'!N45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Net Change in Cash</t>
+        </is>
+      </c>
+      <c r="B46" s="6">
+        <f>'YTD CF'!B46</f>
+        <v/>
+      </c>
+      <c r="C46" s="6">
+        <f>'YTD CF'!C46-'YTD CF'!B46</f>
+        <v/>
+      </c>
+      <c r="D46" s="6">
+        <f>'YTD CF'!D46-'YTD CF'!C46</f>
+        <v/>
+      </c>
+      <c r="E46" s="6">
+        <f>'CASH FLOW'!C48-'YTD CF'!D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="6">
+        <f>'YTD CF'!E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="6">
+        <f>'YTD CF'!F46-'YTD CF'!E46</f>
+        <v/>
+      </c>
+      <c r="H46" s="6">
+        <f>'YTD CF'!G46-'YTD CF'!F46</f>
+        <v/>
+      </c>
+      <c r="I46" s="6">
+        <f>'CASH FLOW'!D48-'YTD CF'!G46</f>
+        <v/>
+      </c>
+      <c r="J46" s="6">
+        <f>'YTD CF'!H46</f>
+        <v/>
+      </c>
+      <c r="K46" s="6">
+        <f>'YTD CF'!I46-'YTD CF'!H46</f>
+        <v/>
+      </c>
+      <c r="L46" s="6">
+        <f>'YTD CF'!J46-'YTD CF'!I46</f>
+        <v/>
+      </c>
+      <c r="M46" s="6">
+        <f>'CASH FLOW'!E48-'YTD CF'!J46</f>
+        <v/>
+      </c>
+      <c r="N46" s="6">
+        <f>'YTD CF'!K46</f>
+        <v/>
+      </c>
+      <c r="O46" s="6">
+        <f>'YTD CF'!L46-'YTD CF'!K46</f>
+        <v/>
+      </c>
+      <c r="P46" s="6">
+        <f>'YTD CF'!M46-'YTD CF'!L46</f>
+        <v/>
+      </c>
+      <c r="Q46" s="6">
+        <f>'CASH FLOW'!F48-'YTD CF'!M46</f>
+        <v/>
+      </c>
+      <c r="R46" s="6">
+        <f>'YTD CF'!N46</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>